--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-628.5%</t>
+          <t>-628.4%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.7%</t>
+          <t>-235.6%</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158925</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.669145017335683</v>
+        <v>-4.668713022879742</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9570189724197606</v>
+        <v>0.9571917702021373</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.11678128144058</v>
+        <v>-0.1163492869846389</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.754964634803434</v>
+        <v>2.755223831476998</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>447.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-628.4%</t>
+          <t>-629.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-280.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-140.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.6%</t>
+          <t>-230.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.5%</t>
+          <t>-167.5%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158925</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705321</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913419</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46683,10 +46683,10 @@
         <v>0.8194182432978634</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.415369354783206</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46706,10 +46706,10 @@
         <v>0.9845494597762967</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.592951223721887</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46729,10 +46729,10 @@
         <v>0.9644546365221136</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4243068646253942</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.614752668713344</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46752,10 +46752,10 @@
         <v>0.9127340045490719</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4243068646253942</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.62076119911027</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46775,10 +46775,10 @@
         <v>1.050983840435095</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2564995073905111</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.800598261243222</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46798,10 +46798,10 @@
         <v>1.012971588954087</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2564995073905111</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.803391882774703</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46821,10 +46821,10 @@
         <v>1.068277674983383</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.1198901632964186</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.886019837622817</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46844,10 +46844,10 @@
         <v>1.010252018594433</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.262655496119069</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.799441114669337</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46867,10 +46867,10 @@
         <v>1.101506771901703</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.262655496119069</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.865776668466157</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46890,10 +46890,10 @@
         <v>0.890803723357164</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.06463730394991463</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.693168456157048</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46913,10 +46913,10 @@
         <v>0.9850502283363765</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.004746622307321147</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.79939309746478</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46936,10 +46936,10 @@
         <v>0.9605817466024305</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.02063590044030134</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.804487266701035</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46959,10 +46959,10 @@
         <v>0.8885826233779304</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.1969736605632307</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.697220591451949</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46982,10 +46982,10 @@
         <v>0.8873499902823481</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.1969736605632307</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.695712209491878</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024957</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47005,10 +47005,10 @@
         <v>0.8845844716959472</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2035446256178237</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.691632497894558</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47028,10 +47028,10 @@
         <v>0.8877660598138561</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2035446256178237</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.691632497894558</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47051,10 +47051,10 @@
         <v>0.8982971673748956</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.1931712492847364</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.704238280722215</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.471841531545086</v>
+        <v>3.718511813914211</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.668713022879742</v>
+        <v>-4.676034286716738</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9571917702021373</v>
+        <v>0.9542632646673388</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1163492869846389</v>
+        <v>-0.06548693949043993</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.755223831476998</v>
+        <v>2.785741239973518</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.4%</t>
+          <t>444.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-629.2%</t>
+          <t>-644.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.8%</t>
+          <t>-287.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-140.6%</t>
+          <t>-139.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-236.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-167.5%</t>
+          <t>-170.9%</t>
         </is>
       </c>
     </row>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.323758884139315</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.03656517016002558</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.105668914512453</v>
+        <v>-7.260529512370967</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1183332784699656</v>
+        <v>0.05638903932656003</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.982377779695322</v>
+        <v>-7.137238377553836</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1651478264073947</v>
+        <v>0.1032035872639891</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.961228580791879</v>
+        <v>-7.116089178650393</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.181308484206097</v>
+        <v>0.1193642450626915</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717463138808434</v>
+        <v>-6.872323736666949</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2745953693465255</v>
+        <v>0.21265113020312</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.570566111090564</v>
+        <v>-6.725426708949078</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3354784943536897</v>
+        <v>0.2735342552102842</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.320715717141489</v>
+        <v>-6.475576315000003</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4281607269170218</v>
+        <v>0.3662164877736163</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.144823624674057</v>
+        <v>-6.299684222532571</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5021166874246434</v>
+        <v>0.4401724482812379</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.973377161651594</v>
+        <v>-6.128237759510108</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5840227786881824</v>
+        <v>0.5220785395447769</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.748344161982771</v>
+        <v>-5.903204759841285</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6730564561720089</v>
+        <v>0.611112217028603</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.684708419748836</v>
+        <v>-5.83956901760735</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7032055541198998</v>
+        <v>0.6412613149764943</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.591708378542938</v>
+        <v>-5.746568976401452</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7215998293860548</v>
+        <v>0.6596555902426493</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.351277881738078</v>
+        <v>-5.506138479596592</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8195151047328761</v>
+        <v>0.7575708655894706</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.279035313566883</v>
+        <v>-5.433895911425397</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8523414458361742</v>
+        <v>0.7903972066927687</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.226036991285495</v>
+        <v>-5.380897589144009</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8742193586660694</v>
+        <v>0.8122751195226638</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.117232105805768</v>
+        <v>-5.272092703664282</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9147393840779539</v>
+        <v>0.8527951449345483</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897211307768758</v>
+        <v>-5.052071905627272</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004326740303372</v>
+        <v>0.9423825011599667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.76434361870548</v>
+        <v>-4.919204216563994</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073367998730506</v>
+        <v>1.011423759587101</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.60482851518611</v>
+        <v>-4.759689113044624</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138319884578556</v>
+        <v>1.076375645435151</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460156370086373</v>
+        <v>-4.615016967944887</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206276845179891</v>
+        <v>1.144332606036486</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.520031197444065</v>
+        <v>-4.674891795302579</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16836440563824</v>
+        <v>1.106420166494834</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433231699665056</v>
+        <v>-4.58809229752357</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.22548469807241</v>
+        <v>1.163540458929004</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435701406126862</v>
+        <v>-4.590562003985376</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.2245692168611</v>
+        <v>1.162624977717694</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504071592450872</v>
+        <v>-4.658932190309386</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208228064806197</v>
+        <v>1.146283825662792</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612609773367006</v>
+        <v>-4.76747037122552</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155249501071635</v>
+        <v>1.09330526192823</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643602932695711</v>
+        <v>-4.798463530554225</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9675618023805399</v>
+        <v>0.9056175632371342</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468128672903243</v>
+        <v>-4.622989270761757</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042318738289315</v>
+        <v>0.9803744991459096</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579064925544492</v>
+        <v>-4.733925523403006</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9736862659940226</v>
+        <v>0.9117420268506171</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782091503087725</v>
+        <v>-4.936952100946239</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8956070201966349</v>
+        <v>0.8336627810532293</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624165904152432</v>
+        <v>-4.779026502010946</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689496462028844</v>
+        <v>0.9070054070594789</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.692783038984568</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983933019872959</v>
+        <v>0.9364490628438902</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.583229260525034</v>
+        <v>-4.738089858383548</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9720463496722296</v>
+        <v>0.9101021105288238</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.612262365227335</v>
+        <v>-4.767122963085849</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9609849808244106</v>
+        <v>0.8990407416810049</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.519451883776475</v>
+        <v>-4.674312481634989</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9273818652961201</v>
+        <v>0.8654376261527146</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.470888831555445</v>
+        <v>-4.625749429413959</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.948680562109133</v>
+        <v>0.8867363229657272</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.358217613319195</v>
+        <v>-4.513078211177709</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.988824757915356</v>
+        <v>0.9268805187719504</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.245840612136522</v>
+        <v>-4.400701209995036</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.039266854219092</v>
+        <v>0.9773226150756869</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.444075181023253</v>
+        <v>-4.598935778881767</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9714702284329391</v>
+        <v>0.9095259892895335</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.527076462048532</v>
+        <v>-4.681937059907046</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7766254360234808</v>
+        <v>0.7146811968800753</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.65414346835552</v>
+        <v>-4.809004066214034</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8459482942198913</v>
+        <v>0.7840040550764855</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.740742051336623</v>
+        <v>-4.895602649195137</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8258218871297731</v>
+        <v>0.7638776479863674</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.702358388778472</v>
+        <v>-4.857218986636986</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8385947934954021</v>
+        <v>0.7766505543519966</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.525242058743306</v>
+        <v>-4.68010265660182</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9061703543547706</v>
+        <v>0.8442261152113648</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.495539934767012</v>
+        <v>-4.650400532625526</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9187345957072011</v>
+        <v>0.8567903565637955</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.316164513528244</v>
+        <v>-4.471025111386759</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9842717395091225</v>
+        <v>0.922327500365717</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.36117872704885</v>
+        <v>-4.516039324907364</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.94707350943247</v>
+        <v>0.8851292702890643</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.628183237321285</v>
+        <v>-4.783043835179799</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8459632676624418</v>
+        <v>0.784019028519036</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.729381018758458</v>
+        <v>-4.884241616616972</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8046880769840741</v>
+        <v>0.7427438378406683</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.696905432587686</v>
+        <v>-4.8517660304462</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8152782730066996</v>
+        <v>0.7533340338632941</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.677867304880388</v>
+        <v>-4.832727902738903</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8194182432978634</v>
+        <v>0.7574740041544579</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.415369354783206</v>
+        <v>2.38045918798449</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.708993936031007</v>
+        <v>-4.863854533889521</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9845494597762967</v>
+        <v>0.922605220632891</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.592951223721887</v>
+        <v>2.55804105692317</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.761314316631799</v>
+        <v>-4.916174914490313</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9644546365221136</v>
+        <v>0.9025103973787079</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4243068646253942</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.614752668713344</v>
+        <v>2.579842501914627</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.905637222556718</v>
+        <v>-5.060497820415232</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9127340045490719</v>
+        <v>0.8507897654056662</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4243068646253942</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.62076119911027</v>
+        <v>2.585851032311553</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.757894252321715</v>
+        <v>-4.912754850180229</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.050983840435095</v>
+        <v>0.9890396012916893</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2564995073905111</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800598261243222</v>
+        <v>2.765688094444505</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.859908934852936</v>
+        <v>-5.01476953271145</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.012971588954087</v>
+        <v>0.9510273498106816</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2564995073905111</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.803391882774703</v>
+        <v>2.768481715975986</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.723299590758844</v>
+        <v>-4.878160188617358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.068277674983383</v>
+        <v>1.006333435839977</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1198901632964186</v>
+        <v>-0.1780737746276131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.886019837622817</v>
+        <v>2.8511096708241</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.866064923581494</v>
+        <v>-5.020925521440008</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010252018594433</v>
+        <v>0.9483077794510275</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.262655496119069</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.799441114669337</v>
+        <v>2.76453094787062</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.803766924805371</v>
+        <v>-4.958627522663885</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101506771901703</v>
+        <v>1.039562532758297</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.262655496119069</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.865776668466157</v>
+        <v>2.830866501667441</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.601976727140213</v>
+        <v>-4.756837324998727</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.890803723357164</v>
+        <v>0.8288594842137584</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.06463730394991463</v>
+        <v>-0.1228209152811092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.693168456157048</v>
+        <v>2.658258289358332</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.54208604549762</v>
+        <v>-4.696946643356134</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9850502283363765</v>
+        <v>0.9231059891929709</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.004746622307321147</v>
+        <v>-0.06293023363851569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.79939309746478</v>
+        <v>2.764482930666063</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.639826590122595</v>
+        <v>-4.794687187981109</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9605817466024305</v>
+        <v>0.8986375074590247</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02063590044030134</v>
+        <v>-0.07881951177149588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.804487266701035</v>
+        <v>2.769577099902318</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.816164350245524</v>
+        <v>-4.971024948104038</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8885826233779304</v>
+        <v>0.8266383842345246</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1969736605632307</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.697220591451949</v>
+        <v>2.662310424653232</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.815474978084301</v>
+        <v>-4.970335575942815</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8873499902823481</v>
+        <v>0.8254057511389425</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1969736605632307</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.695712209491878</v>
+        <v>2.660802042693161</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.822045943138893</v>
+        <v>-4.976906540997407</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8845844716959472</v>
+        <v>0.8226402325525417</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2035446256178237</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.691632497894558</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.814091972844121</v>
+        <v>-4.968952570702635</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8877660598138561</v>
+        <v>0.8258218206704506</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2035446256178237</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.691632497894558</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.803718596511034</v>
+        <v>-4.958579194369548</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8982971673748956</v>
+        <v>0.8363529282314899</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1931712492847364</v>
+        <v>-0.2513548606159309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.704238280722215</v>
+        <v>2.669328113923498</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.718511813914211</v>
+        <v>3.471270409404134</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.676034286716738</v>
+        <v>-4.830894884575252</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9542632646673388</v>
+        <v>0.8923190255239333</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06548693949043993</v>
+        <v>-0.1236705508216345</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785741239973518</v>
+        <v>2.750831073174801</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-53.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>443.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.7%</t>
+          <t>-658.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.0%</t>
+          <t>-292.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-140.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.4%</t>
+          <t>-243.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.9%</t>
+          <t>-188.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1979"/>
+  <dimension ref="A1:G1980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.323758884139315</v>
+        <v>-7.330600661348156</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03656517016002558</v>
+        <v>0.03382845927648903</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.260529512370967</v>
+        <v>-7.267371289579808</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05638903932656003</v>
+        <v>0.05365232844302348</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.137238377553836</v>
+        <v>-7.144080154762677</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1032035872639891</v>
+        <v>0.1004668763804526</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.116089178650393</v>
+        <v>-7.122930955859234</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1193642450626915</v>
+        <v>0.1166275341791554</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.872323736666949</v>
+        <v>-6.879165513875789</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.21265113020312</v>
+        <v>0.2099144193195834</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.725426708949078</v>
+        <v>-6.732268486157919</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2735342552102842</v>
+        <v>0.2707975443267481</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.475576315000003</v>
+        <v>-6.482418092208844</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3662164877736163</v>
+        <v>0.3634797768900797</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.299684222532571</v>
+        <v>-6.306525999741412</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4401724482812379</v>
+        <v>0.4374357373977014</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.128237759510108</v>
+        <v>-6.135079536718949</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5220785395447769</v>
+        <v>0.5193418286612403</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.903204759841285</v>
+        <v>-5.910046537050126</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.611112217028603</v>
+        <v>0.6083755061450669</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.83956901760735</v>
+        <v>-5.846410794816191</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6412613149764943</v>
+        <v>0.6385246040929577</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.746568976401452</v>
+        <v>-5.753410753610293</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6596555902426493</v>
+        <v>0.6569188793591128</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.506138479596592</v>
+        <v>-5.512980256805433</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7575708655894706</v>
+        <v>0.7548341547059341</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.433895911425397</v>
+        <v>-5.440737688634238</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7903972066927687</v>
+        <v>0.7876604958092321</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.380897589144009</v>
+        <v>-5.38773936635285</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8122751195226638</v>
+        <v>0.8095384086391273</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.272092703664282</v>
+        <v>-5.278934480873123</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8527951449345483</v>
+        <v>0.8500584340510118</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.052071905627272</v>
+        <v>-5.058913682836113</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9423825011599667</v>
+        <v>0.9396457902764301</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.919204216563994</v>
+        <v>-4.926045993772835</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.011423759587101</v>
+        <v>1.008687048703564</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.759689113044624</v>
+        <v>-4.766530890253465</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.076375645435151</v>
+        <v>1.073638934551614</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.615016967944887</v>
+        <v>-4.621858745153728</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.144332606036486</v>
+        <v>1.141595895152949</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.674891795302579</v>
+        <v>-4.68173357251142</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.106420166494834</v>
+        <v>1.103683455611298</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.58809229752357</v>
+        <v>-4.594934074732411</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.163540458929004</v>
+        <v>1.160803748045468</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.590562003985376</v>
+        <v>-4.597403781194217</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.162624977717694</v>
+        <v>1.159888266834157</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.658932190309386</v>
+        <v>-4.665773967518227</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.146283825662792</v>
+        <v>1.143547114779256</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.76747037122552</v>
+        <v>-4.774312148434361</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.09330526192823</v>
+        <v>1.090568551044693</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.798463530554225</v>
+        <v>-4.805305307763066</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9056175632371342</v>
+        <v>0.9028808523535978</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.622989270761757</v>
+        <v>-4.629831047970598</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9803744991459096</v>
+        <v>0.9776377882623732</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.733925523403006</v>
+        <v>-4.740767300611846</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9117420268506171</v>
+        <v>0.9090053159670806</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.936952100946239</v>
+        <v>-4.94379387815508</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8336627810532293</v>
+        <v>0.830926070169693</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.779026502010946</v>
+        <v>-4.785868279219787</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9070054070594789</v>
+        <v>0.9042686961759425</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.692783038984568</v>
+        <v>-4.699624816193409</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9364490628438902</v>
+        <v>0.9337123519603538</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.738089858383548</v>
+        <v>-4.744931635592389</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9101021105288238</v>
+        <v>0.9073653996452875</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.767122963085849</v>
+        <v>-4.77396474029469</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8990407416810049</v>
+        <v>0.8963040307974686</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.674312481634989</v>
+        <v>-4.68115425884383</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8654376261527146</v>
+        <v>0.862700915269178</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.625749429413959</v>
+        <v>-4.6325912066228</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8867363229657272</v>
+        <v>0.8839996120821909</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.513078211177709</v>
+        <v>-4.51991998838655</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9268805187719504</v>
+        <v>0.9241438078884139</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.400701209995036</v>
+        <v>-4.407542987203877</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9773226150756869</v>
+        <v>0.9745859041921503</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.598935778881767</v>
+        <v>-4.605777556090608</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9095259892895335</v>
+        <v>0.9067892784059972</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.681937059907046</v>
+        <v>-4.688778837115887</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7146811968800753</v>
+        <v>0.7119444859965389</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.809004066214034</v>
+        <v>-4.815845843422875</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7840040550764855</v>
+        <v>0.7812673441929492</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.895602649195137</v>
+        <v>-4.902444426403978</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7638776479863674</v>
+        <v>0.761140937102831</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.857218986636986</v>
+        <v>-4.864060763845827</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7766505543519966</v>
+        <v>0.7739138434684603</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.68010265660182</v>
+        <v>-4.686944433810661</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8442261152113648</v>
+        <v>0.8414894043278285</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.650400532625526</v>
+        <v>-4.657242309834367</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8567903565637955</v>
+        <v>0.854053645680259</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.471025111386759</v>
+        <v>-4.477866888595599</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.922327500365717</v>
+        <v>0.9195907894821804</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.516039324907364</v>
+        <v>-4.522881102116205</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8851292702890643</v>
+        <v>0.882392559405528</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.783043835179799</v>
+        <v>-4.78988561238864</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.784019028519036</v>
+        <v>0.7812823176354997</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.884241616616972</v>
+        <v>-4.891083393825813</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7427438378406683</v>
+        <v>0.740007126957132</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.8517660304462</v>
+        <v>-4.858607807655041</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7533340338632941</v>
+        <v>0.7505973229797576</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.832727902738903</v>
+        <v>-4.839569679947743</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7574740041544579</v>
+        <v>0.7547372932709215</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.415369354783206</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.863854533889521</v>
+        <v>-4.870696311098362</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.922605220632891</v>
+        <v>0.9198685097493546</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.592951223721887</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.916174914490313</v>
+        <v>-4.923016691699154</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9025103973787079</v>
+        <v>0.8997736864951715</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4243068646253942</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.614752668713344</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.060497820415232</v>
+        <v>-5.067339597624072</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8507897654056662</v>
+        <v>0.8480530545221301</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4243068646253942</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.62076119911027</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.912754850180229</v>
+        <v>-4.91959662738907</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9890396012916893</v>
+        <v>0.9863028904081528</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2564995073905111</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.800598261243222</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.01476953271145</v>
+        <v>-5.021611309920291</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9510273498106816</v>
+        <v>0.9482906389271455</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2564995073905111</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.803391882774703</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.878160188617358</v>
+        <v>-4.885001965826199</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.006333435839977</v>
+        <v>1.003596724956441</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.1198901632964186</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.886019837622817</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.020925521440008</v>
+        <v>-5.027767298648849</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9483077794510275</v>
+        <v>0.945571068567491</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.262655496119069</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.799441114669337</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.958627522663885</v>
+        <v>-4.965469299872726</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.039562532758297</v>
+        <v>1.036825821874761</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.262655496119069</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.865776668466157</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.756837324998727</v>
+        <v>-4.763679102207568</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8288594842137584</v>
+        <v>0.8261227733302219</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.06463730394991463</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.693168456157048</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.696946643356134</v>
+        <v>-4.703788420564975</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9231059891929709</v>
+        <v>0.9203692783094346</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.004746622307321147</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.79939309746478</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.794687187981109</v>
+        <v>-4.80152896518995</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8986375074590247</v>
+        <v>0.8959007965754884</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.02063590044030134</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.804487266701035</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.971024948104038</v>
+        <v>-4.977866725312879</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8266383842345246</v>
+        <v>0.8239016733509883</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.1969736605632307</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.697220591451949</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.970335575942815</v>
+        <v>-4.977177353151656</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8254057511389425</v>
+        <v>0.8226690402554062</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.1969736605632307</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.695712209491878</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.976906540997407</v>
+        <v>-4.983748318206248</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8226402325525417</v>
+        <v>0.8199035216690054</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2035446256178237</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.691632497894558</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.968952570702635</v>
+        <v>-4.975794347911476</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8258218206704506</v>
+        <v>0.8230851097869141</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2035446256178237</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.691632497894558</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.958579194369548</v>
+        <v>-4.965420971578389</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8363529282314899</v>
+        <v>0.8336162173479535</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.1931712492847364</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.704238280722215</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,45 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.471270409404134</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.830894884575252</v>
+        <v>-4.969588461444923</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8923190255239333</v>
+        <v>0.8368415947760648</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1236705508216345</v>
+        <v>-0.1973387391512706</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.750831073174801</v>
+        <v>2.706630160177019</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="2" t="n">
+        <v>45442</v>
+      </c>
+      <c r="B1980" t="n">
+        <v>3.467601119972448</v>
+      </c>
+      <c r="C1980" t="n">
+        <v>2.580827728222232</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>-4.969588461444923</v>
+      </c>
+      <c r="E1980" t="n">
+        <v>0.8368415947760648</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>-0.1973387391512706</v>
+      </c>
+      <c r="G1980" t="n">
+        <v>2.5738915252086</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.7%</t>
+          <t>444.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.5%</t>
+          <t>-644.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-292.5%</t>
+          <t>-287.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-140.6%</t>
+          <t>-139.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-243.7%</t>
+          <t>-236.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390588</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297402</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.330600661348156</v>
+        <v>-7.323758884139315</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03382845927648903</v>
+        <v>0.03656517016002558</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.267371289579808</v>
+        <v>-7.260529512370967</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05365232844302348</v>
+        <v>0.05638903932656003</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.144080154762677</v>
+        <v>-7.137238377553836</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1004668763804526</v>
+        <v>0.1032035872639891</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.122930955859234</v>
+        <v>-7.116089178650393</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1166275341791554</v>
+        <v>0.1193642450626915</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.879165513875789</v>
+        <v>-6.872323736666949</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2099144193195834</v>
+        <v>0.21265113020312</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732268486157919</v>
+        <v>-6.725426708949078</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2707975443267481</v>
+        <v>0.2735342552102842</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.482418092208844</v>
+        <v>-6.475576315000003</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3634797768900797</v>
+        <v>0.3662164877736163</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.306525999741412</v>
+        <v>-6.299684222532571</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4374357373977014</v>
+        <v>0.4401724482812379</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135079536718949</v>
+        <v>-6.128237759510108</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5193418286612403</v>
+        <v>0.5220785395447769</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.910046537050126</v>
+        <v>-5.903204759841285</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6083755061450669</v>
+        <v>0.611112217028603</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.846410794816191</v>
+        <v>-5.83956901760735</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6385246040929577</v>
+        <v>0.6412613149764943</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.753410753610293</v>
+        <v>-5.746568976401452</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6569188793591128</v>
+        <v>0.6596555902426493</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.512980256805433</v>
+        <v>-5.506138479596592</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7548341547059341</v>
+        <v>0.7575708655894706</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.440737688634238</v>
+        <v>-5.433895911425397</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7876604958092321</v>
+        <v>0.7903972066927687</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.38773936635285</v>
+        <v>-5.380897589144009</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8095384086391273</v>
+        <v>0.8122751195226638</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.278934480873123</v>
+        <v>-5.272092703664282</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8500584340510118</v>
+        <v>0.8527951449345483</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.058913682836113</v>
+        <v>-5.052071905627272</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9396457902764301</v>
+        <v>0.9423825011599667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.926045993772835</v>
+        <v>-4.919204216563994</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.008687048703564</v>
+        <v>1.011423759587101</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.766530890253465</v>
+        <v>-4.759689113044624</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.073638934551614</v>
+        <v>1.076375645435151</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.621858745153728</v>
+        <v>-4.615016967944887</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.141595895152949</v>
+        <v>1.144332606036486</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.68173357251142</v>
+        <v>-4.674891795302579</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.103683455611298</v>
+        <v>1.106420166494834</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.594934074732411</v>
+        <v>-4.58809229752357</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.160803748045468</v>
+        <v>1.163540458929004</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.597403781194217</v>
+        <v>-4.590562003985376</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.159888266834157</v>
+        <v>1.162624977717694</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.665773967518227</v>
+        <v>-4.658932190309386</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.143547114779256</v>
+        <v>1.146283825662792</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.774312148434361</v>
+        <v>-4.76747037122552</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.090568551044693</v>
+        <v>1.09330526192823</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.805305307763066</v>
+        <v>-4.798463530554225</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9028808523535978</v>
+        <v>0.9056175632371342</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.629831047970598</v>
+        <v>-4.622989270761757</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9776377882623732</v>
+        <v>0.9803744991459096</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.740767300611846</v>
+        <v>-4.733925523403006</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9090053159670806</v>
+        <v>0.9117420268506171</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.94379387815508</v>
+        <v>-4.936952100946239</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.830926070169693</v>
+        <v>0.8336627810532293</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.785868279219787</v>
+        <v>-4.779026502010946</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9042686961759425</v>
+        <v>0.9070054070594789</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.699624816193409</v>
+        <v>-4.692783038984568</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9337123519603538</v>
+        <v>0.9364490628438902</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.744931635592389</v>
+        <v>-4.738089858383548</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9073653996452875</v>
+        <v>0.9101021105288238</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.77396474029469</v>
+        <v>-4.767122963085849</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8963040307974686</v>
+        <v>0.8990407416810049</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.68115425884383</v>
+        <v>-4.674312481634989</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.862700915269178</v>
+        <v>0.8654376261527146</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.6325912066228</v>
+        <v>-4.625749429413959</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8839996120821909</v>
+        <v>0.8867363229657272</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.51991998838655</v>
+        <v>-4.513078211177709</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9241438078884139</v>
+        <v>0.9268805187719504</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.407542987203877</v>
+        <v>-4.400701209995036</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9745859041921503</v>
+        <v>0.9773226150756869</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.605777556090608</v>
+        <v>-4.598935778881767</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9067892784059972</v>
+        <v>0.9095259892895335</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.688778837115887</v>
+        <v>-4.681937059907046</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7119444859965389</v>
+        <v>0.7146811968800753</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.815845843422875</v>
+        <v>-4.809004066214034</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7812673441929492</v>
+        <v>0.7840040550764855</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.902444426403978</v>
+        <v>-4.895602649195137</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.761140937102831</v>
+        <v>0.7638776479863674</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.864060763845827</v>
+        <v>-4.857218986636986</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7739138434684603</v>
+        <v>0.7766505543519966</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.686944433810661</v>
+        <v>-4.68010265660182</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8414894043278285</v>
+        <v>0.8442261152113648</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.657242309834367</v>
+        <v>-4.650400532625526</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.854053645680259</v>
+        <v>0.8567903565637955</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.477866888595599</v>
+        <v>-4.471025111386759</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9195907894821804</v>
+        <v>0.922327500365717</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.522881102116205</v>
+        <v>-4.516039324907364</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.882392559405528</v>
+        <v>0.8851292702890643</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.78988561238864</v>
+        <v>-4.783043835179799</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7812823176354997</v>
+        <v>0.784019028519036</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.891083393825813</v>
+        <v>-4.884241616616972</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.740007126957132</v>
+        <v>0.7427438378406683</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.858607807655041</v>
+        <v>-4.8517660304462</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7505973229797576</v>
+        <v>0.7533340338632941</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.839569679947743</v>
+        <v>-4.832727902738903</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7547372932709215</v>
+        <v>0.7574740041544579</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.415369354783206</v>
+        <v>2.38045918798449</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.870696311098362</v>
+        <v>-4.863854533889521</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9198685097493546</v>
+        <v>0.922605220632891</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.592951223721887</v>
+        <v>2.55804105692317</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.923016691699154</v>
+        <v>-4.916174914490313</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8997736864951715</v>
+        <v>0.9025103973787079</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4243068646253942</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.614752668713344</v>
+        <v>2.579842501914627</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.067339597624072</v>
+        <v>-5.060497820415232</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8480530545221301</v>
+        <v>0.8507897654056662</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4243068646253942</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.62076119911027</v>
+        <v>2.585851032311553</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.91959662738907</v>
+        <v>-4.912754850180229</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9863028904081528</v>
+        <v>0.9890396012916893</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2564995073905111</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800598261243222</v>
+        <v>2.765688094444505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.021611309920291</v>
+        <v>-5.01476953271145</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9482906389271455</v>
+        <v>0.9510273498106816</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2564995073905111</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.803391882774703</v>
+        <v>2.768481715975986</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.885001965826199</v>
+        <v>-4.878160188617358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.003596724956441</v>
+        <v>1.006333435839977</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1198901632964186</v>
+        <v>-0.1780737746276131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.886019837622817</v>
+        <v>2.8511096708241</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.027767298648849</v>
+        <v>-5.020925521440008</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.945571068567491</v>
+        <v>0.9483077794510275</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.262655496119069</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.799441114669337</v>
+        <v>2.76453094787062</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.965469299872726</v>
+        <v>-4.958627522663885</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.036825821874761</v>
+        <v>1.039562532758297</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.262655496119069</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.865776668466157</v>
+        <v>2.830866501667441</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.763679102207568</v>
+        <v>-4.756837324998727</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8261227733302219</v>
+        <v>0.8288594842137584</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.06463730394991463</v>
+        <v>-0.1228209152811092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.693168456157048</v>
+        <v>2.658258289358332</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.703788420564975</v>
+        <v>-4.696946643356134</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9203692783094346</v>
+        <v>0.9231059891929709</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.004746622307321147</v>
+        <v>-0.06293023363851569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.79939309746478</v>
+        <v>2.764482930666063</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.80152896518995</v>
+        <v>-4.794687187981109</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8959007965754884</v>
+        <v>0.8986375074590247</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02063590044030134</v>
+        <v>-0.07881951177149588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.804487266701035</v>
+        <v>2.769577099902318</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.977866725312879</v>
+        <v>-4.971024948104038</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8239016733509883</v>
+        <v>0.8266383842345246</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1969736605632307</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.697220591451949</v>
+        <v>2.662310424653232</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.977177353151656</v>
+        <v>-4.970335575942815</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8226690402554062</v>
+        <v>0.8254057511389425</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1969736605632307</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.695712209491878</v>
+        <v>2.660802042693161</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.983748318206248</v>
+        <v>-4.976906540997407</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8199035216690054</v>
+        <v>0.8226402325525417</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2035446256178237</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.691632497894558</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.975794347911476</v>
+        <v>-4.968952570702635</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8230851097869141</v>
+        <v>0.8258218206704506</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2035446256178237</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.691632497894558</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.965420971578389</v>
+        <v>-4.958579194369548</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8336162173479535</v>
+        <v>0.8363529282314899</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1931712492847364</v>
+        <v>-0.2513548606159309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.704238280722215</v>
+        <v>2.669328113923498</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.969588461444923</v>
+        <v>-4.830894884575252</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8368415947760648</v>
+        <v>0.8923190255239333</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1973387391512706</v>
+        <v>-0.1236705508216345</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.706630160177019</v>
+        <v>2.750831073174801</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.467601119972448</v>
+        <v>3.467601119972447</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.580827728222232</v>
+        <v>2.580827728222233</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.969588461444923</v>
+        <v>-4.830894884575252</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8368415947760648</v>
+        <v>0.8923190255239333</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1973387391512706</v>
+        <v>-0.1236705508216345</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.5738915252086</v>
+        <v>2.573891525208601</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-33.8%</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-664.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>447.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.7%</t>
+          <t>-643.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-266.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.0%</t>
+          <t>-286.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-188.6%</t>
+          <t>-168.9%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.2250880661980107</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.208168991656733</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.1768657993509272</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.192960067539566</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>-0.06026569249886787</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.13304855529719</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>-0.05522810177128135</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.133641031773562</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.2178541817359199</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.047336981411444</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.283621571785332</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.02204763452215</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4962344954519427</v>
+        <v>-0.4888662488425766</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.927630497043261</v>
+        <v>2.930577795687007</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5780063958796944</v>
+        <v>-0.5706381492703283</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.885004462827399</v>
+        <v>2.887951761471145</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.637847257142206</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.865833435156096</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-0.8454130415338179</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.780631917518692</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.263167065080655</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.61145719960502</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.466456534402458</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.530007628475221</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.674460592755535</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.451698149687915</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-1.88587301364351</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.362214637670713</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.225031391232032</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.219635585941754</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.433522172683717</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.156577563099848</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.680723357448938</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>2.065795839602328</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.173108385473035</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.869948220436421</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.558288776403108</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.714418602877255</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-3.901971549629771</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.578714617041207</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.108483326516792</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.492215964942656</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.364324412295485</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.391652457331438</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.796130205445272</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.205263027538928</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.030824199577824</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.099670204887997</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.366486846808277</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9639857376517815</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.73011309170859</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8250227999258977</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.095240474347337</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6782263618762303</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.503829251528016</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.513552395018718</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.780405351843848</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3981073873638454</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.196797226130846</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2295446882579242</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.513409168671494</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.1131586019103437</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-7.859283990656303</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>-0.02909176173788497</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-8.022863868840687</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.09611879295663739</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.319525210650886</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.2110043537515085</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.531924638034567</v>
+        <v>-8.524556391425202</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2999904292393847</v>
+        <v>-0.2970431305956382</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.914926026777199</v>
+        <v>-8.907557780167833</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4532930860580211</v>
+        <v>-0.4503457874142747</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.096795817762233</v>
+        <v>-9.089427571152868</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5234694864806047</v>
+        <v>-0.5205221878368587</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.456326140266235</v>
+        <v>-9.448957893656869</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.661931312184155</v>
+        <v>-0.658984013540409</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.506675203720457</v>
+        <v>-9.499306957111092</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6741549176086665</v>
+        <v>-0.6712076189649205</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.604294481141853</v>
+        <v>-9.596926234532487</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.710160877955456</v>
+        <v>-0.70721357931171</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.751820569147496</v>
+        <v>-9.74445232253813</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.766277756836141</v>
+        <v>-0.763330458192395</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.95607874447736</v>
+        <v>-9.948710497867994</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8424678298494443</v>
+        <v>-0.8395205312056979</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09788851868415</v>
+        <v>-10.09052027207478</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8947091850477231</v>
+        <v>-0.8917618864039771</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0244186870167</v>
+        <v>-10.01705044040733</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8499495508873229</v>
+        <v>-0.8470022522435761</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19954310440324</v>
+        <v>-10.19217485779388</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9054440970944233</v>
+        <v>-0.9024967984506773</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43399519841773</v>
+        <v>-10.42662695180837</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.006444099601815</v>
+        <v>-1.003496800958068</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.7144307963456</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.125290529546941</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.76721695194593</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.145289201948515</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-10.99924587168219</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.235407041213905</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-10.94723035771338</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.210610499939979</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-11.0889021994375</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.268754463528369</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-11.03931135501267</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.233864715593562</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.84015924777557</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.167255006345406</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.61431409505616</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.067337872221433</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.48973543871856</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-1.016367265130337</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.54263072676285</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-1.034891606185944</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.2587219958341</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.9155944095758075</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.18735560322445</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.8967851149258141</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-9.923518736020384</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.8011338493570936</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.656276935151986</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.6960716895091084</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.558369896475496</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.6572091890119731</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.534416355499538</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.6469592664760961</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.270356417176741</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.5545956073087295</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.563276793671903</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.2745507915670955</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.523092495305713</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.258133448332778</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.443022699767909</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.2267387088968995</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.209541477538309</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.1254217911672071</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-8.059875086530795</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.06844744507716083</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-7.927599612899908</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>-0.02016976887777888</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.736999938226756</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>0.05888516167911861</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.422433702788455</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.488000139543175</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.1713914223762099</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.422433702788455</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.593590129316279</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>0.001179496867749208</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.528023692561559</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.612325031434876</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>0.04222987789739685</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.528023692561559</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.464384990027277</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>-0.018473028227731</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.507702776653002</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.447226839895983</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>-0.02032375442869139</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.490544626521707</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.403678433125292</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>-0.009865003815508366</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.490544626521707</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.323758884139315</v>
+        <v>-7.316390637529948</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03656517016002558</v>
+        <v>0.03951246880377246</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.260529512370967</v>
+        <v>-7.2531612657616</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05638903932656003</v>
+        <v>0.05933633797030691</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.137238377553836</v>
+        <v>-7.129870130944469</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1032035872639891</v>
+        <v>0.106150885907736</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.116089178650393</v>
+        <v>-7.108720932041026</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1193642450626915</v>
+        <v>0.1223115437064384</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.872323736666949</v>
+        <v>-6.864955490057581</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.21265113020312</v>
+        <v>0.2155984288468669</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.725426708949078</v>
+        <v>-6.718058462339711</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2735342552102842</v>
+        <v>0.2764815538540311</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.475576315000003</v>
+        <v>-6.468208068390636</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3662164877736163</v>
+        <v>0.3691637864173631</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.299684222532571</v>
+        <v>-6.292315975923204</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4401724482812379</v>
+        <v>0.4431197469249848</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.128237759510108</v>
+        <v>-6.12086951290074</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5220785395447769</v>
+        <v>0.5250258381885238</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.903204759841285</v>
+        <v>-5.895836513231917</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.611112217028603</v>
+        <v>0.6140595156723498</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.83956901760735</v>
+        <v>-5.832200770997983</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6412613149764943</v>
+        <v>0.6442086136202412</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.746568976401452</v>
+        <v>-5.739200729792085</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6596555902426493</v>
+        <v>0.6626028888863962</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.506138479596592</v>
+        <v>-5.498770232987225</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7575708655894706</v>
+        <v>0.7605181642332175</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.433895911425397</v>
+        <v>-5.42652766481603</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7903972066927687</v>
+        <v>0.7933445053365156</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.380897589144009</v>
+        <v>-5.373529342534642</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8122751195226638</v>
+        <v>0.8152224181664107</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.272092703664282</v>
+        <v>-5.264724457054915</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8527951449345483</v>
+        <v>0.8557424435782952</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.052071905627272</v>
+        <v>-5.044703659017904</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9423825011599667</v>
+        <v>0.9453297998037136</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.919204216563994</v>
+        <v>-4.911835969954627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.011423759587101</v>
+        <v>1.014371058230848</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.759689113044624</v>
+        <v>-4.752320866435257</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.076375645435151</v>
+        <v>1.079322944078898</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.615016967944887</v>
+        <v>-4.60764872133552</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.144332606036486</v>
+        <v>1.147279904680232</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.674891795302579</v>
+        <v>-4.667523548693212</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.106420166494834</v>
+        <v>1.109367465138581</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.58809229752357</v>
+        <v>-4.580724050914203</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.163540458929004</v>
+        <v>1.166487757572751</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.590562003985376</v>
+        <v>-4.583193757376009</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.162624977717694</v>
+        <v>1.165572276361441</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.658932190309386</v>
+        <v>-4.651563943700019</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.146283825662792</v>
+        <v>1.149231124306539</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.76747037122552</v>
+        <v>-4.760102124616153</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.09330526192823</v>
+        <v>1.096252560571976</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.798463530554225</v>
+        <v>-4.791095283944858</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9056175632371342</v>
+        <v>0.908564861880881</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.622989270761757</v>
+        <v>-4.615621024152389</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9803744991459096</v>
+        <v>0.9833217977896564</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.733925523403006</v>
+        <v>-4.726557276793638</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9117420268506171</v>
+        <v>0.914689325494364</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.936952100946239</v>
+        <v>-4.929583854336872</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8336627810532293</v>
+        <v>0.8366100796969762</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.779026502010946</v>
+        <v>-4.771658255401579</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9070054070594789</v>
+        <v>0.9099527057032257</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.692783038984568</v>
+        <v>-4.685414792375201</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9364490628438902</v>
+        <v>0.9393963614876371</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.738089858383548</v>
+        <v>-4.730721611774181</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9101021105288238</v>
+        <v>0.9130494091725707</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.767122963085849</v>
+        <v>-4.759754716476482</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8990407416810049</v>
+        <v>0.9019880403247518</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.674312481634989</v>
+        <v>-4.666944235025622</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8654376261527146</v>
+        <v>0.8683849247964615</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.625749429413959</v>
+        <v>-4.618381182804592</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8867363229657272</v>
+        <v>0.8896836216094741</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.513078211177709</v>
+        <v>-4.505709964568342</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9268805187719504</v>
+        <v>0.9298278174156973</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.400701209995036</v>
+        <v>-4.393332963385669</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9773226150756869</v>
+        <v>0.9802699137194337</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.598935778881767</v>
+        <v>-4.5915675322724</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9095259892895335</v>
+        <v>0.9124732879332804</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.681937059907046</v>
+        <v>-4.674568813297679</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7146811968800753</v>
+        <v>0.7176284955238221</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.809004066214034</v>
+        <v>-4.801635819604667</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7840040550764855</v>
+        <v>0.7869513537202324</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.895602649195137</v>
+        <v>-4.88823440258577</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7638776479863674</v>
+        <v>0.7668249466301142</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.857218986636986</v>
+        <v>-4.849850740027619</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7766505543519966</v>
+        <v>0.7795978529957435</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.68010265660182</v>
+        <v>-4.672734409992453</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8442261152113648</v>
+        <v>0.8471734138551117</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.650400532625526</v>
+        <v>-4.643032286016159</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8567903565637955</v>
+        <v>0.8597376552075424</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.471025111386759</v>
+        <v>-4.463656864777391</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.922327500365717</v>
+        <v>0.9252747990094639</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.516039324907364</v>
+        <v>-4.508671078297997</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8851292702890643</v>
+        <v>0.8880765689328112</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.783043835179799</v>
+        <v>-4.775675588570432</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.784019028519036</v>
+        <v>0.7869663271627829</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.884241616616972</v>
+        <v>-4.876873370007605</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7427438378406683</v>
+        <v>0.7456911364844152</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.8517660304462</v>
+        <v>-4.844397783836833</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7533340338632941</v>
+        <v>0.756281332507041</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.832727902738903</v>
+        <v>-4.825359656129535</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7574740041544579</v>
+        <v>0.7604213027982047</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.5174373359654609</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.863854533889521</v>
+        <v>-4.856486287280154</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.922605220632891</v>
+        <v>0.9255525192766378</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.5174373359654609</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.916174914490313</v>
+        <v>-4.908806667880945</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9025103973787079</v>
+        <v>0.9054576960224547</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4824904759565888</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.060497820415232</v>
+        <v>-5.053129573805864</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8507897654056662</v>
+        <v>0.8537370640494131</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4824904759565888</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.912754850180229</v>
+        <v>-4.905386603570862</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9890396012916893</v>
+        <v>0.9919868999354362</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3146831187217056</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.01476953271145</v>
+        <v>-5.007401286102083</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9510273498106816</v>
+        <v>0.9539746484544285</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3146831187217056</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.878160188617358</v>
+        <v>-4.87079194200799</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.006333435839977</v>
+        <v>1.009280734483724</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1780737746276131</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.020925521440008</v>
+        <v>-5.013557274830641</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9483077794510275</v>
+        <v>0.9512550780947744</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3208391074502636</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.958627522663885</v>
+        <v>-4.951259276054518</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.039562532758297</v>
+        <v>1.042509831402044</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3208391074502636</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.756837324998727</v>
+        <v>-4.74946907838936</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8288594842137584</v>
+        <v>0.8318067828575053</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1228209152811092</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.696946643356134</v>
+        <v>-4.689578396746767</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9231059891929709</v>
+        <v>0.9260532878367178</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.06293023363851569</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.794687187981109</v>
+        <v>-4.787318941371741</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8986375074590247</v>
+        <v>0.9015848061027716</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.07881951177149588</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.971024948104038</v>
+        <v>-4.963656701494671</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8266383842345246</v>
+        <v>0.8295856828782715</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2551572718944253</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.970335575942815</v>
+        <v>-4.962967329333448</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8254057511389425</v>
+        <v>0.8283530497826894</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2551572718944253</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.976906540997407</v>
+        <v>-4.96953829438804</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8226402325525417</v>
+        <v>0.8255875311962886</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2617282369490182</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.968952570702635</v>
+        <v>-4.961584324093268</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8258218206704506</v>
+        <v>0.8287691193141975</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2617282369490182</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.958579194369548</v>
+        <v>-4.951210947760181</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8363529282314899</v>
+        <v>0.8393002268752368</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.2513548606159309</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.82270724432688</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.830894884575252</v>
+        <v>-4.823526637965885</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8923190255239333</v>
+        <v>0.8952663241676801</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.1236705508216345</v>
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.467601119972447</v>
+        <v>3.808002216889278</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.580827728222233</v>
+        <v>2.7783548626527</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.830894884575252</v>
+        <v>-4.823526637965885</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8923190255239333</v>
+        <v>0.8952663241676801</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1236705508216345</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.573891525208601</v>
+        <v>2.771418659639068</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-664.7%</t>
+          <t>-664.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>447.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.9%</t>
+          <t>-627.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.3%</t>
+          <t>-266.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.7%</t>
+          <t>-280.2%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2250880661980107</v>
+        <v>0.2320547962898439</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.208168991656733</v>
+        <v>3.210955683693467</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1768657993509272</v>
+        <v>0.1838325294427604</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.192960067539566</v>
+        <v>3.195746759576299</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06026569249886787</v>
+        <v>-0.05329896240703469</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.13304855529719</v>
+        <v>3.135835247333923</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.05522810177128135</v>
+        <v>-0.04826137167944816</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.133641031773562</v>
+        <v>3.136427723810296</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2178541817359199</v>
+        <v>-0.2108874516440867</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.047336981411444</v>
+        <v>3.050123673448177</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.283621571785332</v>
+        <v>-0.2766548416934988</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.02204763452215</v>
+        <v>3.024834326558883</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4888662488425766</v>
+        <v>-0.4818995187507434</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.930577795687007</v>
+        <v>2.933364487723741</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5706381492703283</v>
+        <v>-0.5636714191784951</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.887951761471145</v>
+        <v>2.890738453507878</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.637847257142206</v>
+        <v>-0.6308805270503728</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.865833435156096</v>
+        <v>2.86862012719283</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8454130415338179</v>
+        <v>-0.8384463114419847</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.780631917518692</v>
+        <v>2.783418609555425</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.263167065080655</v>
+        <v>-1.256200334988822</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.61145719960502</v>
+        <v>2.614243891641753</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.466456534402458</v>
+        <v>-1.459489804310624</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.530007628475221</v>
+        <v>2.532794320511954</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.674460592755535</v>
+        <v>-1.667493862663701</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.451698149687915</v>
+        <v>2.454484841724649</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.88587301364351</v>
+        <v>-1.878906283551677</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.362214637670713</v>
+        <v>2.365001329707447</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.225031391232032</v>
+        <v>-2.218064661140199</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.219635585941754</v>
+        <v>2.222422277978487</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.433522172683717</v>
+        <v>-2.426555442591883</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.156577563099848</v>
+        <v>2.159364255136581</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.680723357448938</v>
+        <v>-2.673756627357105</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.065795839602328</v>
+        <v>2.068582531639061</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.173108385473035</v>
+        <v>-3.166141655381202</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.869948220436421</v>
+        <v>1.872734912473155</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.558288776403108</v>
+        <v>-3.551322046311274</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.714418602877255</v>
+        <v>1.717205294913989</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.901971549629771</v>
+        <v>-3.895004819537937</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.578714617041207</v>
+        <v>1.58150130907794</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.108483326516792</v>
+        <v>-4.101516596424958</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.492215964942656</v>
+        <v>1.495002656979389</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.364324412295485</v>
+        <v>-4.357357682203651</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.391652457331438</v>
+        <v>1.394439149368172</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.796130205445272</v>
+        <v>-4.789163475353439</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.205263027538928</v>
+        <v>1.208049719575661</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.030824199577824</v>
+        <v>-5.023857469485991</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.099670204887997</v>
+        <v>1.102456896924731</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.366486846808277</v>
+        <v>-5.359520116716443</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9639857376517815</v>
+        <v>0.9667724296885152</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.73011309170859</v>
+        <v>-5.723146361616757</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8250227999258977</v>
+        <v>0.8278094919626313</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.095240474347337</v>
+        <v>-6.088273744255503</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6782263618762303</v>
+        <v>0.681013053912964</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.503829251528016</v>
+        <v>-6.496862521436181</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.513552395018718</v>
+        <v>0.5163390870554516</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.780405351843848</v>
+        <v>-6.773438621752014</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3981073873638454</v>
+        <v>0.4008940794005795</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.196797226130846</v>
+        <v>-7.189830496039011</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2295446882579242</v>
+        <v>0.2323313802946578</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.513409168671494</v>
+        <v>-7.50644243857966</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1131586019103437</v>
+        <v>0.1159452939470773</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.859283990656303</v>
+        <v>-7.852317260564469</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02909176173788497</v>
+        <v>-0.02630506970115087</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.022863868840687</v>
+        <v>-8.015897138748853</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09611879295663739</v>
+        <v>-0.09333210091990374</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.319525210650886</v>
+        <v>-8.312558480559051</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2110043537515085</v>
+        <v>-0.2082176617147748</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.524556391425202</v>
+        <v>-8.517589661333368</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2970431305956382</v>
+        <v>-0.2942564385589046</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.907557780167833</v>
+        <v>-8.900591050075999</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4503457874142747</v>
+        <v>-0.447559095377541</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.089427571152868</v>
+        <v>-9.082460841061033</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5205221878368587</v>
+        <v>-0.517735495800125</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.448957893656869</v>
+        <v>-9.441991163565035</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.658984013540409</v>
+        <v>-0.6561973215036754</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.499306957111092</v>
+        <v>-9.492340227019257</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6712076189649205</v>
+        <v>-0.6684209269281864</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.596926234532487</v>
+        <v>-9.589959504440653</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.70721357931171</v>
+        <v>-0.7044268872749764</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.74445232253813</v>
+        <v>-9.737485592446296</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.763330458192395</v>
+        <v>-0.7605437661556613</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.948710497867994</v>
+        <v>-9.94174376777616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8395205312056979</v>
+        <v>-0.8367338391689643</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09052027207478</v>
+        <v>-10.08355354198295</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8917618864039771</v>
+        <v>-0.888975194367243</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.01705044040733</v>
+        <v>-10.0100837103155</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8470022522435761</v>
+        <v>-0.8442155602068429</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19217485779388</v>
+        <v>-10.18520812770204</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9024967984506773</v>
+        <v>-0.8997101064139432</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.42662695180837</v>
+        <v>-10.41966022171653</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.003496800958068</v>
+        <v>-1.000710108921335</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7144307963456</v>
+        <v>-10.70746406625377</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.125290529546941</v>
+        <v>-1.122503837510207</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.76721695194593</v>
+        <v>-10.7602502218541</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.145289201948515</v>
+        <v>-1.142502509911781</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.99924587168219</v>
+        <v>-10.99227914159036</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.235407041213905</v>
+        <v>-1.232620349177171</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.94723035771338</v>
+        <v>-10.94026362762155</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.210610499939979</v>
+        <v>-1.207823807903245</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0889021994375</v>
+        <v>-11.08193546934567</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.268754463528369</v>
+        <v>-1.265967771491635</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.03931135501267</v>
+        <v>-11.03234462492083</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.233864715593562</v>
+        <v>-1.231078023556829</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84015924777557</v>
+        <v>-10.83319251768373</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.167255006345406</v>
+        <v>-1.164468314308672</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.61431409505616</v>
+        <v>-10.60734736496432</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.067337872221433</v>
+        <v>-1.064551180184699</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.48973543871856</v>
+        <v>-10.48276870862673</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.016367265130337</v>
+        <v>-1.013580573093604</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54263072676285</v>
+        <v>-10.53566399667102</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.034891606185944</v>
+        <v>-1.032104914149211</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.2587219958341</v>
+        <v>-10.25175526574227</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9155944095758075</v>
+        <v>-0.9128077175390752</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18735560322445</v>
+        <v>-10.18038887313262</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8967851149258141</v>
+        <v>-0.8939984228890809</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.923518736020384</v>
+        <v>-9.916552005928551</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8011338493570936</v>
+        <v>-0.7983471573203609</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.656276935151986</v>
+        <v>-9.649310205060154</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6960716895091084</v>
+        <v>-0.6932849974723756</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.558369896475496</v>
+        <v>-9.551403166383663</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6572091890119731</v>
+        <v>-0.6544224969752399</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.534416355499538</v>
+        <v>-9.527449625407705</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6469592664760961</v>
+        <v>-0.6441725744393634</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.270356417176741</v>
+        <v>-9.263389687084908</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5545956073087295</v>
+        <v>-0.5518089152719967</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.563276793671903</v>
+        <v>-8.556310063580071</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2745507915670955</v>
+        <v>-0.2717640995303627</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.523092495305713</v>
+        <v>-8.51612576521388</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.258133448332778</v>
+        <v>-0.2553467562960452</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.443022699767909</v>
+        <v>-8.436055969676076</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2267387088968995</v>
+        <v>-0.2239520168601663</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.209541477538309</v>
+        <v>-8.202574747446477</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1254217911672071</v>
+        <v>-0.1226350991304743</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.059875086530795</v>
+        <v>-8.052908356438962</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.06844744507716083</v>
+        <v>-0.06566075304042762</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.927599612899908</v>
+        <v>-7.920632882808076</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02016976887777888</v>
+        <v>-0.01738307684104612</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.736999938226756</v>
+        <v>-7.730033208134923</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05888516167911861</v>
+        <v>0.06167185371585182</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.422433702788455</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.488000139543175</v>
+        <v>-7.481033409451342</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1713914223762099</v>
+        <v>0.1741781144129431</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.422433702788455</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.593590129316279</v>
+        <v>-7.586623399224447</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.001179496867749208</v>
+        <v>0.003966188904482415</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.528023692561559</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.612325031434876</v>
+        <v>-7.605358301343044</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04222987789739685</v>
+        <v>0.04501656993413006</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.528023692561559</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.464384990027277</v>
+        <v>-7.457418259935444</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.018473028227731</v>
+        <v>-0.0156863361909978</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.507702776653002</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.447226839895983</v>
+        <v>-7.44026010980415</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02032375442869139</v>
+        <v>-0.01753706239195818</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.490544626521707</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.403678433125292</v>
+        <v>-7.39671170303346</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.009865003815508366</v>
+        <v>-0.007078311778775159</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.490544626521707</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.316390637529948</v>
+        <v>-7.154563309579602</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03951246880377246</v>
+        <v>0.1042433999839112</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.2531612657616</v>
+        <v>-7.091333937811253</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05933633797030691</v>
+        <v>0.1240672691504452</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.129870130944469</v>
+        <v>-6.968042802994122</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.106150885907736</v>
+        <v>0.1708818170878748</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.108720932041026</v>
+        <v>-6.946893604090679</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1223115437064384</v>
+        <v>0.1870424748865771</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.864955490057581</v>
+        <v>-6.703128162107235</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2155984288468669</v>
+        <v>0.2803293600270056</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.718058462339711</v>
+        <v>-6.556231134389364</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2764815538540311</v>
+        <v>0.3412124850341698</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.468208068390636</v>
+        <v>-6.306380740440289</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3691637864173631</v>
+        <v>0.4338947175975019</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.292315975923204</v>
+        <v>-6.130488647972857</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4431197469249848</v>
+        <v>0.5078506781051235</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.12086951290074</v>
+        <v>-5.959042184950394</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5250258381885238</v>
+        <v>0.5897567693686625</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.895836513231917</v>
+        <v>-5.734009185281571</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6140595156723498</v>
+        <v>0.6787904468524886</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.832200770997983</v>
+        <v>-5.670373443047636</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6442086136202412</v>
+        <v>0.7089395448003799</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739200729792085</v>
+        <v>-5.577373401841738</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626028888863962</v>
+        <v>0.7273338200665345</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498770232987225</v>
+        <v>-5.336942905036878</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605181642332175</v>
+        <v>0.8252490954133562</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42652766481603</v>
+        <v>-5.264700336865683</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7933445053365156</v>
+        <v>0.8580754365166543</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373529342534642</v>
+        <v>-5.211702014584295</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8152224181664107</v>
+        <v>0.8799533493465495</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264724457054915</v>
+        <v>-5.102897129104568</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8557424435782952</v>
+        <v>0.9204733747584335</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044703659017904</v>
+        <v>-4.882876331067558</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9453297998037136</v>
+        <v>1.010060730983852</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911835969954627</v>
+        <v>-4.75000864200428</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014371058230848</v>
+        <v>1.079101989410986</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.752320866435257</v>
+        <v>-4.59049353848491</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.079322944078898</v>
+        <v>1.144053875259036</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.60764872133552</v>
+        <v>-4.445821393385173</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.147279904680232</v>
+        <v>1.212010835860371</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.667523548693212</v>
+        <v>-4.505696220742865</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.109367465138581</v>
+        <v>1.17409839631872</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.580724050914203</v>
+        <v>-4.418896722963856</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.166487757572751</v>
+        <v>1.23121868875289</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.583193757376009</v>
+        <v>-4.421366429425662</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.165572276361441</v>
+        <v>1.230303207541579</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.651563943700019</v>
+        <v>-4.489736615749672</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.149231124306539</v>
+        <v>1.213962055486677</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.760102124616153</v>
+        <v>-4.598274796665806</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.096252560571976</v>
+        <v>1.160983491752115</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.791095283944858</v>
+        <v>-4.629267955994512</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.908564861880881</v>
+        <v>0.9732957930610198</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.615621024152389</v>
+        <v>-4.453793696202043</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9833217977896564</v>
+        <v>1.048052728969795</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.726557276793638</v>
+        <v>-4.564729948843292</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.914689325494364</v>
+        <v>0.9794202566745025</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.929583854336872</v>
+        <v>-4.767756526386525</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8366100796969762</v>
+        <v>0.9013410108771147</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.771658255401579</v>
+        <v>-4.609830927451232</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9099527057032257</v>
+        <v>0.9746836368833645</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.685414792375201</v>
+        <v>-4.523587464424854</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9393963614876371</v>
+        <v>1.004127292667776</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.730721611774181</v>
+        <v>-4.568894283823834</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9130494091725707</v>
+        <v>0.9777803403527094</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.759754716476482</v>
+        <v>-4.597927388526135</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9019880403247518</v>
+        <v>0.9667189715048905</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.666944235025622</v>
+        <v>-4.505116907075275</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8683849247964615</v>
+        <v>0.9331158559766</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.618381182804592</v>
+        <v>-4.456553854854246</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8896836216094741</v>
+        <v>0.9544145527896128</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.505709964568342</v>
+        <v>-4.343882636617995</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9298278174156973</v>
+        <v>0.9945587485958358</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.393332963385669</v>
+        <v>-4.231505635435322</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9802699137194337</v>
+        <v>1.045000844899572</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.5915675322724</v>
+        <v>-4.429740204322053</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9124732879332804</v>
+        <v>0.9772042191134189</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.674568813297679</v>
+        <v>-4.512741485347332</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7176284955238221</v>
+        <v>0.7823594267039606</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.801635819604667</v>
+        <v>-4.63980849165432</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7869513537202324</v>
+        <v>0.8516822849003711</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.88823440258577</v>
+        <v>-4.726407074635423</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7668249466301142</v>
+        <v>0.831555877810253</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.849850740027619</v>
+        <v>-4.688023412077272</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7795978529957435</v>
+        <v>0.844328784175882</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.672734409992453</v>
+        <v>-4.510907082042106</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8471734138551117</v>
+        <v>0.9119043450352504</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.643032286016159</v>
+        <v>-4.481204958065812</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8597376552075424</v>
+        <v>0.9244685863876809</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.463656864777391</v>
+        <v>-4.301829536827045</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9252747990094639</v>
+        <v>0.9900057301896024</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.508671078297997</v>
+        <v>-4.34684375034765</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8880765689328112</v>
+        <v>0.9528075001129499</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.775675588570432</v>
+        <v>-4.613848260620085</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7869663271627829</v>
+        <v>0.8516972583429216</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.876873370007605</v>
+        <v>-4.715046042057258</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7456911364844152</v>
+        <v>0.8104220676645539</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.844397783836833</v>
+        <v>-4.682570455886486</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.756281332507041</v>
+        <v>0.8210122636871795</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.825359656129535</v>
+        <v>-4.663532328179189</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7604213027982047</v>
+        <v>0.8251522339783435</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.5174373359654609</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.856486287280154</v>
+        <v>-4.694658959329807</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9255525192766378</v>
+        <v>0.9902834504567766</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.5174373359654609</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.908806667880945</v>
+        <v>-4.746979339930599</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9054576960224547</v>
+        <v>0.9701886272025935</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4824904759565888</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.053129573805864</v>
+        <v>-4.891302245855518</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8537370640494131</v>
+        <v>0.9184679952295518</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4824904759565888</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.905386603570862</v>
+        <v>-4.743559275620515</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9919868999354362</v>
+        <v>1.056717831115575</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3146831187217056</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.007401286102083</v>
+        <v>-4.845573958151737</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9539746484544285</v>
+        <v>1.018705579634567</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3146831187217056</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.87079194200799</v>
+        <v>-4.708964614057644</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.009280734483724</v>
+        <v>1.074011665663863</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1780737746276131</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.013557274830641</v>
+        <v>-4.851729946880294</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9512550780947744</v>
+        <v>1.015986009274913</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3208391074502636</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.951259276054518</v>
+        <v>-4.789431948104172</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.042509831402044</v>
+        <v>1.107240762582183</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3208391074502636</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.74946907838936</v>
+        <v>-4.587641750439014</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8318067828575053</v>
+        <v>0.8965377140376438</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1228209152811092</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.689578396746767</v>
+        <v>-4.52775106879642</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9260532878367178</v>
+        <v>0.9907842190168563</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.06293023363851569</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.787318941371741</v>
+        <v>-4.625491613421395</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9015848061027716</v>
+        <v>0.9663157372829103</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.07881951177149588</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.963656701494671</v>
+        <v>-4.801829373544324</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8295856828782715</v>
+        <v>0.8943166140584102</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2551572718944253</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.962967329333448</v>
+        <v>-4.801140001383101</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8283530497826894</v>
+        <v>0.8930839809628282</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2551572718944253</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.96953829438804</v>
+        <v>-4.807710966437694</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8255875311962886</v>
+        <v>0.8903184623764271</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2617282369490182</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.961584324093268</v>
+        <v>-4.799756996142921</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8287691193141975</v>
+        <v>0.893500050494336</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2617282369490182</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.951210947760181</v>
+        <v>-4.789383619809835</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8393002268752368</v>
+        <v>0.9040311580553755</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.2513548606159309</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.823526637965885</v>
+        <v>-4.661699310015538</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8952663241676801</v>
+        <v>0.9599972553478189</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.1236705508216345</v>
@@ -47091,10 +47091,10 @@
         <v>2.7783548626527</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.823526637965885</v>
+        <v>-4.661699310015538</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8952663241676801</v>
+        <v>0.9599972553478189</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1236705508216345</v>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-664.0%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.3%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.7%</t>
+          <t>-630.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.0%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.2%</t>
+          <t>-282.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-143.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.4%</t>
+          <t>-253.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.9%</t>
+          <t>-182.4%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2320547962898439</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.210955683693467</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1838325294427604</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.195746759576299</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.05329896240703469</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.135835247333923</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.04826137167944816</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.136427723810296</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2108874516440867</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.050123673448177</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2766548416934988</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.024834326558883</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4818995187507434</v>
+        <v>-0.4962344954519427</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.933364487723741</v>
+        <v>2.927630497043261</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5636714191784951</v>
+        <v>-0.5780063958796944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.890738453507878</v>
+        <v>2.885004462827399</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6308805270503728</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86862012719283</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8384463114419847</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.783418609555425</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.256200334988822</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.614243891641753</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.459489804310624</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.532794320511954</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.667493862663701</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.454484841724649</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.878906283551677</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.365001329707447</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.218064661140199</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.222422277978487</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.426555442591883</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.159364255136581</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.673756627357105</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.068582531639061</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.166141655381202</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.872734912473155</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.551322046311274</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.717205294913989</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.895004819537937</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.58150130907794</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.101516596424958</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.495002656979389</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.357357682203651</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.394439149368172</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.789163475353439</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.208049719575661</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.023857469485991</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.102456896924731</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.359520116716443</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9667724296885152</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.723146361616757</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8278094919626313</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.088273744255503</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.681013053912964</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.496862521436181</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5163390870554516</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.773438621752014</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4008940794005795</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.189830496039011</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2323313802946578</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.50644243857966</v>
+        <v>-7.520777415280859</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1159452939470773</v>
+        <v>0.1102113032665977</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.852317260564469</v>
+        <v>-7.866652237265669</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02630506970115087</v>
+        <v>-0.03203906038163096</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.015897138748853</v>
+        <v>-8.030232115450053</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09333210091990374</v>
+        <v>-0.09906609160038382</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.312558480559051</v>
+        <v>-8.326893457260251</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2082176617147748</v>
+        <v>-0.2139516523952549</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.517589661333368</v>
+        <v>-8.531924638034567</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2942564385589046</v>
+        <v>-0.2999904292393847</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.900591050075999</v>
+        <v>-8.914926026777199</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.447559095377541</v>
+        <v>-0.4532930860580211</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.082460841061033</v>
+        <v>-9.096795817762233</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.517735495800125</v>
+        <v>-0.5234694864806047</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.441991163565035</v>
+        <v>-9.456326140266235</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6561973215036754</v>
+        <v>-0.661931312184155</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.492340227019257</v>
+        <v>-9.506675203720457</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6684209269281864</v>
+        <v>-0.6741549176086665</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.589959504440653</v>
+        <v>-9.604294481141853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7044268872749764</v>
+        <v>-0.710160877955456</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.737485592446296</v>
+        <v>-9.751820569147496</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7605437661556613</v>
+        <v>-0.766277756836141</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.03504431600112</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.94174376777616</v>
+        <v>-9.95607874447736</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8367338391689643</v>
+        <v>-0.8424678298494443</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.162683260615109</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.08355354198295</v>
+        <v>-10.09788851868415</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.888975194367243</v>
+        <v>-0.8947091850477231</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.333962058260685</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0100837103155</v>
+        <v>-10.0244186870167</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8442155602068429</v>
+        <v>-0.8499495508873229</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.260492226593236</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.18520812770204</v>
+        <v>-10.19954310440324</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8997101064139432</v>
+        <v>-0.9054440970944233</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.43561664397978</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.41966022171653</v>
+        <v>-10.43399519841773</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.000710108921335</v>
+        <v>-1.006444099601815</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.43561664397978</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.70746406625377</v>
+        <v>-10.72179904295497</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.122503837510207</v>
+        <v>-1.128237828190687</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.723420488517018</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7602502218541</v>
+        <v>-10.7745851985553</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.142502509911781</v>
+        <v>-1.148236500592261</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.819095975099415</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.99227914159036</v>
+        <v>-11.00661411829156</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.232620349177171</v>
+        <v>-1.238354339857651</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.881108672287839</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.94026362762155</v>
+        <v>-10.95459860432275</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.207823807903245</v>
+        <v>-1.213557798583725</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.881108672287839</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.08193546934567</v>
+        <v>-11.09627044604687</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.265967771491635</v>
+        <v>-1.271701762172115</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.881108672287839</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.03234462492083</v>
+        <v>-11.04667960162203</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.231078023556829</v>
+        <v>-1.236812014237309</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.831517827863005</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.83319251768373</v>
+        <v>-10.84752749438493</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.164468314308672</v>
+        <v>-1.170202304989152</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.666195301913191</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.60734736496432</v>
+        <v>-10.62168234166552</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.064551180184699</v>
+        <v>-1.070285170865179</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.624268626326028</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.48276870862673</v>
+        <v>-10.49710368532793</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.013580573093604</v>
+        <v>-1.019314563774083</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.624268626326028</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.53566399667102</v>
+        <v>-10.54999897337222</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.032104914149211</v>
+        <v>-1.037838904829691</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.619313280237582</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25175526574227</v>
+        <v>-10.26609024244347</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9128077175390752</v>
+        <v>-0.9185417082195544</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.619313280237582</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18038887313262</v>
+        <v>-10.19472384983382</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8939984228890809</v>
+        <v>-0.899732413569561</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.547946887627934</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.916552005928551</v>
+        <v>-9.930886982629751</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7983471573203609</v>
+        <v>-0.8040811480008405</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.547946887627934</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.649310205060154</v>
+        <v>-9.663645181761353</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6932849974723756</v>
+        <v>-0.6990189881528552</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.547946887627934</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.551403166383663</v>
+        <v>-9.565738143084863</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6544224969752399</v>
+        <v>-0.66015648765572</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.479961137767377</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.527449625407705</v>
+        <v>-9.541784602108905</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6441725744393634</v>
+        <v>-0.649906565119843</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.45600759679142</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.263389687084908</v>
+        <v>-9.277724663786108</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5518089152719967</v>
+        <v>-0.5575429059524764</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.191947658468624</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.556310063580071</v>
+        <v>-8.570645040281271</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2717640995303627</v>
+        <v>-0.2774980902108424</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.191947658468624</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.51612576521388</v>
+        <v>-8.53046074191508</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2553467562960452</v>
+        <v>-0.2610807469765248</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.151763360102433</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.436055969676076</v>
+        <v>-8.450390946377276</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2239520168601663</v>
+        <v>-0.2296860075406464</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.071693564564629</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.202574747446477</v>
+        <v>-8.216909724147676</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1226350991304743</v>
+        <v>-0.128369089810954</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.838212342335031</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.052908356438962</v>
+        <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.06566075304042762</v>
+        <v>-0.07139474372090771</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.920632882808076</v>
+        <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.01738307684104612</v>
+        <v>-0.02311706752152576</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.730033208134923</v>
+        <v>-7.744368184836123</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06167185371585182</v>
+        <v>0.05593786303537174</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.422433702788455</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.481033409451342</v>
+        <v>-7.495368386152542</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1741781144129431</v>
+        <v>0.168444123732463</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.422433702788455</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.586623399224447</v>
+        <v>-7.600958375925646</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.003966188904482415</v>
+        <v>-0.001767801775997668</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.528023692561559</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.605358301343044</v>
+        <v>-7.619693278044243</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04501656993413006</v>
+        <v>0.03928257925364997</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.528023692561559</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.457418259935444</v>
+        <v>-7.471753236636644</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0156863361909978</v>
+        <v>-0.02142032687147788</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.507702776653002</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.44026010980415</v>
+        <v>-7.45459508650535</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01753706239195818</v>
+        <v>-0.02327105307243826</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.490544626521707</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.39671170303346</v>
+        <v>-7.411046679734659</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.007078311778775159</v>
+        <v>-0.01281230245925524</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.490544626521707</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.154563309579602</v>
+        <v>-7.168898286280801</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1042433999839112</v>
+        <v>0.09850940930343111</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.091333937811253</v>
+        <v>-7.105668914512453</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1240672691504452</v>
+        <v>0.1183332784699656</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.968042802994122</v>
+        <v>-6.982377779695322</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1708818170878748</v>
+        <v>0.1651478264073947</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.946893604090679</v>
+        <v>-6.961228580791879</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1870424748865771</v>
+        <v>0.181308484206097</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.703128162107235</v>
+        <v>-6.717463138808434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2803293600270056</v>
+        <v>0.2745953693465255</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.556231134389364</v>
+        <v>-6.570566111090564</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3412124850341698</v>
+        <v>0.3354784943536897</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.306380740440289</v>
+        <v>-6.320715717141489</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4338947175975019</v>
+        <v>0.4281607269170218</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.130488647972857</v>
+        <v>-6.144823624674057</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5078506781051235</v>
+        <v>0.5021166874246434</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.959042184950394</v>
+        <v>-5.973377161651594</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5897567693686625</v>
+        <v>0.5840227786881824</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.734009185281571</v>
+        <v>-5.748344161982771</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6787904468524886</v>
+        <v>0.6730564561720089</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.670373443047636</v>
+        <v>-5.684708419748836</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7089395448003799</v>
+        <v>0.7032055541198998</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.577373401841738</v>
+        <v>-5.591708378542938</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7273338200665345</v>
+        <v>0.7215998293860548</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.336942905036878</v>
+        <v>-5.351277881738078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8252490954133562</v>
+        <v>0.8195151047328761</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.264700336865683</v>
+        <v>-5.279035313566883</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8580754365166543</v>
+        <v>0.8523414458361742</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.211702014584295</v>
+        <v>-5.226036991285495</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8799533493465495</v>
+        <v>0.8742193586660694</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.102897129104568</v>
+        <v>-5.117232105805768</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9204733747584335</v>
+        <v>0.9147393840779539</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.882876331067558</v>
+        <v>-4.897211307768758</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.010060730983852</v>
+        <v>1.004326740303372</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.75000864200428</v>
+        <v>-4.76434361870548</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.079101989410986</v>
+        <v>1.073367998730506</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.59049353848491</v>
+        <v>-4.60482851518611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.144053875259036</v>
+        <v>1.138319884578556</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.445821393385173</v>
+        <v>-4.460156370086373</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.212010835860371</v>
+        <v>1.206276845179891</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.505696220742865</v>
+        <v>-4.520031197444065</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.17409839631872</v>
+        <v>1.16836440563824</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.418896722963856</v>
+        <v>-4.433231699665056</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.23121868875289</v>
+        <v>1.22548469807241</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.421366429425662</v>
+        <v>-4.435701406126862</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.230303207541579</v>
+        <v>1.2245692168611</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.489736615749672</v>
+        <v>-4.504071592450872</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.213962055486677</v>
+        <v>1.208228064806197</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.598274796665806</v>
+        <v>-4.612609773367006</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.160983491752115</v>
+        <v>1.155249501071635</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.629267955994512</v>
+        <v>-4.643602932695711</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9732957930610198</v>
+        <v>0.9675618023805399</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.453793696202043</v>
+        <v>-4.468128672903243</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.048052728969795</v>
+        <v>1.042318738289315</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.564729948843292</v>
+        <v>-4.579064925544492</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9794202566745025</v>
+        <v>0.9736862659940226</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.767756526386525</v>
+        <v>-4.782091503087725</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9013410108771147</v>
+        <v>0.8956070201966349</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.609830927451232</v>
+        <v>-4.624165904152432</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9746836368833645</v>
+        <v>0.9689496462028844</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.523587464424854</v>
+        <v>-4.537922441126054</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.004127292667776</v>
+        <v>0.9983933019872959</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.568894283823834</v>
+        <v>-4.583229260525034</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9777803403527094</v>
+        <v>0.9720463496722296</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.597927388526135</v>
+        <v>-4.612262365227335</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9667189715048905</v>
+        <v>0.9609849808244106</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.505116907075275</v>
+        <v>-4.631351918162129</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9331158559766</v>
+        <v>0.8826218515418587</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3012520902883266</v>
+        <v>-0.4131521246739802</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554767788947462</v>
+        <v>2.48762776831607</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.456553854854246</v>
+        <v>-4.582788865941099</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9544145527896128</v>
+        <v>0.9039205483548713</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2526890380672964</v>
+        <v>-0.36458907245295</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.585779096204681</v>
+        <v>2.518639075573288</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.343882636617995</v>
+        <v>-4.470117647704849</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9945587485958358</v>
+        <v>0.9440647441610945</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.2519178542166998</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.648457535658154</v>
+        <v>2.581317515026762</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.231505635435322</v>
+        <v>-4.357740646522176</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.045000844899572</v>
+        <v>0.994506840464831</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.2519178542166998</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.653948831488821</v>
+        <v>2.586808810857429</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.429740204322053</v>
+        <v>-4.555975215408907</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9772042191134189</v>
+        <v>0.9267102146786776</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3382523887177767</v>
+        <v>-0.4501524231034304</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.546505291925322</v>
+        <v>2.47936527129393</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.512741485347332</v>
+        <v>-4.638976496434186</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7823594267039606</v>
+        <v>0.7318654222692194</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4687233076306042</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.373718481209671</v>
+        <v>2.306578460578279</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.63980849165432</v>
+        <v>-4.766043502741174</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8516822849003711</v>
+        <v>0.8011882804656296</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4687233076306042</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.493868141928877</v>
+        <v>2.426728121297484</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.726407074635423</v>
+        <v>-4.852642085722277</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.831555877810253</v>
+        <v>0.7810618733755115</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.4687233076306042</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.5083811680312</v>
+        <v>2.441241147399807</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.688023412077272</v>
+        <v>-4.814258423164126</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.844328784175882</v>
+        <v>0.7938347797411407</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.430339645072453</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.528830806908459</v>
+        <v>2.461690786277067</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.510907082042106</v>
+        <v>-4.63714209312896</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9119043450352504</v>
+        <v>0.8614103406005089</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.430339645072453</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.525559835753761</v>
+        <v>2.458419815122368</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.481204958065812</v>
+        <v>-4.607439969152666</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9244685863876809</v>
+        <v>0.8739745819529396</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3229097359021127</v>
+        <v>-0.4348097702877664</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.523561152386486</v>
+        <v>2.456421131755094</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.301829536827045</v>
+        <v>-4.428064547913898</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9900057301896024</v>
+        <v>0.9395117257548611</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.166132977731394</v>
+        <v>-0.2780330121170477</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.611414182595332</v>
+        <v>2.544274161963939</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.34684375034765</v>
+        <v>-4.473078761434504</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9528075001129499</v>
+        <v>0.9023134956782084</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1964818730459986</v>
+        <v>-0.3083819074316523</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.574012300738159</v>
+        <v>2.506872280106766</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.613848260620085</v>
+        <v>-4.740083271706939</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8516972583429216</v>
+        <v>0.8012032539081801</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3908449110889472</v>
+        <v>-0.5027449454746009</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.463086040251335</v>
+        <v>2.395946019619943</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.715046042057258</v>
+        <v>-4.841281053144112</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8104220676645539</v>
+        <v>0.7599280632298124</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.57115375901992</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.421244674020645</v>
+        <v>2.354104653389253</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.682570455886486</v>
+        <v>-4.80880546697334</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8210122636871795</v>
+        <v>0.7705182592524382</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.57115375901992</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.418844635574962</v>
+        <v>2.35170461494357</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.663532328179189</v>
+        <v>-4.789767339266042</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8251522339783435</v>
+        <v>0.774658229543602</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6293373703511146</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.313319167353098</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.694658959329807</v>
+        <v>-4.820893970416661</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9902834504567766</v>
+        <v>0.9397894460220351</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.6293373703511146</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.490901036291778</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.746979339930599</v>
+        <v>-4.873214351017452</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9701886272025935</v>
+        <v>0.919694622767852</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.5943905103422424</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.512702481283235</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.891302245855518</v>
+        <v>-5.017537256942371</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9184679952295518</v>
+        <v>0.8679739907948103</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.5943905103422424</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.518711011680161</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.743559275620515</v>
+        <v>-4.869794286707369</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.056717831115575</v>
+        <v>1.006223826680833</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4265831531073593</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.698548073813113</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.845573958151737</v>
+        <v>-4.97180896923859</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.018705579634567</v>
+        <v>0.9682115751998257</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.4265831531073593</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.701341695344594</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.708964614057644</v>
+        <v>-4.835199625144497</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.074011665663863</v>
+        <v>1.023517661229121</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.2899738090132668</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.783969650192708</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.851729946880294</v>
+        <v>-4.977964957967147</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.015986009274913</v>
+        <v>0.9654920048401714</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4327391418359172</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.697390927239228</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.789431948104172</v>
+        <v>-4.915666959191025</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.107240762582183</v>
+        <v>1.056746758147441</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.4327391418359172</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.763726481036048</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.587641750439014</v>
+        <v>-4.713876761525867</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8965377140376438</v>
+        <v>0.8460437096029025</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.2347209496667628</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.591118268726939</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.52775106879642</v>
+        <v>-4.653986079883274</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9907842190168563</v>
+        <v>0.940290214582115</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.1748302680241693</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.697342910034671</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.625491613421395</v>
+        <v>-4.751726624508248</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9663157372829103</v>
+        <v>0.9158217328481688</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.1907195461571495</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.702437079270926</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.801829373544324</v>
+        <v>-4.928064384631178</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8943166140584102</v>
+        <v>0.8438226096236687</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.3670573062800789</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.59517040402184</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.801140001383101</v>
+        <v>-4.927375012469954</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8930839809628282</v>
+        <v>0.8425899765280866</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.3670573062800789</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.593662022061769</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.807710966437694</v>
+        <v>-4.933945977524547</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8903184623764271</v>
+        <v>0.8398244579416858</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.3736282713346719</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.589582310464449</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.799756996142921</v>
+        <v>-4.925992007229775</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.893500050494336</v>
+        <v>0.8430060460595947</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.3736282713346719</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.589582310464449</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.789383619809835</v>
+        <v>-4.915618630896688</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9040311580553755</v>
+        <v>0.853537153620634</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.3632548950015846</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.602188093292106</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82270724432688</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.661699310015538</v>
+        <v>-4.787934321102392</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9599972553478189</v>
+        <v>0.9095032509130774</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1236705508216345</v>
+        <v>-0.2355705852072881</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.750831073174801</v>
+        <v>2.683691052543409</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.808002216889278</v>
+        <v>3.511965621676836</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.7783548626527</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.661699310015538</v>
+        <v>-4.687564729023019</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9599972553478189</v>
+        <v>0.9364057602206988</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1236705508216345</v>
+        <v>-0.29181095500698</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771418659639068</v>
+        <v>2.636701503139466</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240530.xlsx
+++ b/tame_output/ON/bt/strategyON_20240530.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-680.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>456.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.3%</t>
+          <t>-634.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-272.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.6%</t>
+          <t>-284.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-307.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-143.3%</t>
+          <t>-154.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-253.2%</t>
+          <t>-254.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-184.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.4%</t>
+          <t>-182.9%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.02058598758163421</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.130448142831849</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.508251432830725</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.027521031811378</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>-0.2165455042681609</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.070536630589473</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.508251432830725</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.06246211630892</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>-0.2115079135405744</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.071129107065846</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.563895889097042</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.094426230254047</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.3741339935052129</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>2.984825056703727</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.55018137429233</v>
+        <v>1.401269809132403</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.064943902994957</v>
+        <v>3.975596963899002</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.439901383554625</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>2.959535709814432</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.55018137429233</v>
+        <v>1.401269809132403</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.065961512125428</v>
+        <v>3.976614573029472</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4962344954519427</v>
+        <v>-0.6451460606118695</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.927630497043261</v>
+        <v>2.86806587097929</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.55018137429233</v>
+        <v>1.401269809132403</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.056589544113184</v>
+        <v>3.967242605017227</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5780063958796944</v>
+        <v>-0.7269179610396213</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.885004462827399</v>
+        <v>2.825439836763428</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.577216947698467</v>
+        <v>1.42830538253854</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.062893614112104</v>
+        <v>3.973546675016148</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.794127068911499</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.803321510448379</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.577216947698467</v>
+        <v>1.42830538253854</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.067658930945806</v>
+        <v>3.97831199184985</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-1.001692853303111</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.718119992810974</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.369651163306855</v>
+        <v>1.220739598146928</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940944256430079</v>
+        <v>3.851597317334123</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.419446876849948</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.548945274897303</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>0.802985574600091</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.598871794711084</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.622736346171751</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.467495703767504</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9899765505255895</v>
+        <v>0.8410649853656628</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.710932596865305</v>
+        <v>3.621585657769349</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.830740404524828</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.389186224980198</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9899765505255895</v>
+        <v>0.8410649853656628</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.71582474141923</v>
+        <v>3.626477802323274</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-2.042152825412803</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.299702712962996</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7785641296376145</v>
+        <v>0.6296525644776877</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.584058745224433</v>
+        <v>3.494711806128477</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.381311203001325</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.157123661234036</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4394057520490924</v>
+        <v>0.2904941868891656</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.373648017977769</v>
+        <v>3.284301078881813</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.589801984453009</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.094065638392131</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.230914970597408</v>
+        <v>0.08200340543748119</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.268891838845527</v>
+        <v>3.179544899749571</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.837003169218231</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>2.003283914894611</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2510683240962204</v>
+        <v>0.1021567589362936</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.289082601353383</v>
+        <v>3.199735662257427</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.329388197242328</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.807436295728704</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.3902282690878031</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.994757976582657</v>
+        <v>2.905411037486701</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.7145685881724</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.651906678169539</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.3902282690878031</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.993300515395521</v>
+        <v>2.903953576299564</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-4.058251361399063</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.51620269233349</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3492227559550946</v>
+        <v>-0.4981343211150213</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.930326007633806</v>
+        <v>2.84097906853785</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.264763138286084</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.429704040234939</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.7046460980020428</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.802525000157851</v>
+        <v>2.713178061061894</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.520604224064777</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.329140532623721</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.7046460980020428</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.80429792685811</v>
+        <v>2.714950987762154</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.952410017214564</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.142751102831211</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.692152029283383</v>
+        <v>-0.8410635944433098</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.708780316460754</v>
+        <v>2.619433377364798</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.187104011347117</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.037158280180281</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.8347273272140546</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700866851800398</v>
+        <v>2.611519912704442</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.522766658577569</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9014738129440647</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.8347273272140546</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699447443456363</v>
+        <v>2.610100504360407</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.886392903477883</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.7625108752181808</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.9329489640811804</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.557655082474373</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.251520286116629</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6157144371685135</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-1.229259748380193</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.379123126900797</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.660109063297307</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.4510404703110016</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.132731404607149</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.93668516361314</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3355954626561291</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.12791683707861</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.353077037900137</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.1670327635502074</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.125910887687487</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.669688980440785</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.05064667720262728</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.136169578356166</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-8.015563802425595</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>-0.09160368644560135</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.132269143501861</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-8.179143680609979</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.1586307176643542</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.637848525560871</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.130674063556862</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.475805022420177</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.2735162784592253</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.70659166129475</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.093207158045743</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.531924638034567</v>
+        <v>-8.680836203194493</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2999904292393847</v>
+        <v>-0.3595550553033551</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.70659166129475</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.08918085351134</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.914926026777199</v>
+        <v>-9.063837591937125</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4532930860580211</v>
+        <v>-0.5128577121219915</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.70659166129475</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.089078752189756</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.096795817762233</v>
+        <v>-9.245707382922159</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5234694864806047</v>
+        <v>-0.583034112544575</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.739549887119858</v>
+        <v>-1.888461452279785</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.071875332666121</v>
+        <v>1.982528393570165</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.456326140266235</v>
+        <v>-9.605237705426161</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.661931312184155</v>
+        <v>-0.7214959382481254</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.739549887119858</v>
+        <v>-1.888461452279785</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.077225635964171</v>
+        <v>1.987878696868215</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.506675203720457</v>
+        <v>-9.655586768880383</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6741549176086665</v>
+        <v>-0.7337195436726369</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.78989895057408</v>
+        <v>-1.938810515734007</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.054932217848815</v>
+        <v>1.96558527875286</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.604294481141853</v>
+        <v>-9.753206046301779</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.710160877955456</v>
+        <v>-0.7697255040194264</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.887518227995477</v>
+        <v>-2.036429793155404</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.999402402017747</v>
+        <v>1.91005546292179</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.751820569147496</v>
+        <v>-9.900732134307422</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.766277756836141</v>
+        <v>-0.8258423829001114</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.03504431600112</v>
+        <v>-2.183955881161048</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.913780305535933</v>
+        <v>1.824433366439976</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.95607874447736</v>
+        <v>-10.10499030963729</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8424678298494443</v>
+        <v>-0.9020324559134147</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.162683260615109</v>
+        <v>-2.311594825775037</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.842710135886182</v>
+        <v>1.753363196790225</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09788851868415</v>
+        <v>-10.24680008384407</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8947091850477231</v>
+        <v>-0.9542738111116935</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.333962058260685</v>
+        <v>-2.482873623420612</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.744425411783272</v>
+        <v>1.655078472687316</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0244186870167</v>
+        <v>-10.17333025217662</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8499495508873229</v>
+        <v>-0.9095141769512933</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.260492226593236</v>
+        <v>-2.409403791753164</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.803879012277163</v>
+        <v>1.714532073181206</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19954310440324</v>
+        <v>-10.34845466956317</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9054440970944233</v>
+        <v>-0.9650087231583937</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.584528209139707</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.713359582592753</v>
+        <v>1.624012643496797</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43399519841773</v>
+        <v>-10.58290676357766</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.006444099601815</v>
+        <v>-1.066008725665786</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.584528209139707</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.706140417691157</v>
+        <v>1.616793478595201</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.8707106081149</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.187802454254657</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.723420488517018</v>
+        <v>-2.872332053676946</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526785920194838</v>
+        <v>1.437438981098882</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.92349676371522</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.207801126656231</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.819095975099415</v>
+        <v>-2.968007540259343</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.470496418083956</v>
+        <v>1.381149478988</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-11.15552568345148</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.297918965921621</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.881108672287839</v>
+        <v>-3.030020237447766</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.435982528400017</v>
+        <v>1.346635589304061</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-11.10351016948267</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.273122424647696</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.881108672287839</v>
+        <v>-3.030020237447766</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.439972864086418</v>
+        <v>1.350625924990462</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-11.24518201120679</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.331266388236085</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.881108672287839</v>
+        <v>-3.030020237447766</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.438497637187676</v>
+        <v>1.34915069809172</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-11.19559116678196</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.29637664030128</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.831517827863005</v>
+        <v>-2.980429393022932</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.483305554007449</v>
+        <v>1.393958614911492</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.99643905954486</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.229766931053123</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.666195301913191</v>
+        <v>-2.815106867073119</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.569447935930654</v>
+        <v>1.480100996834697</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.77059390682545</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.129849796929149</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.773180191485955</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.60418301431916</v>
+        <v>1.514836075223204</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.64601525048785</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-1.078879189838054</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.773180191485955</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.605322158875219</v>
+        <v>1.515975219779263</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.69891053853214</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-1.09740353089366</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.768224845397509</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.610929140690395</v>
+        <v>1.521582201594438</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.41500180760339</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.9781063342835248</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.768224845397509</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.616662844929031</v>
+        <v>1.527315905833075</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.34363541499375</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.9592970396335305</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.696858452787861</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.649745418100955</v>
+        <v>1.560398479004999</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-10.07979854778968</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.86364577406481</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.696858452787861</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.639861936788047</v>
+        <v>1.550514997692091</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.812556746921278</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.7585836142168252</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.696858452787861</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.638027376288673</v>
+        <v>1.548680437192717</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.714649708244787</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.7197211137196895</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.479961137767377</v>
+        <v>-2.628872702927304</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.678518511231546</v>
+        <v>1.58917157213559</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.690696167268829</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.709471191183813</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.45600759679142</v>
+        <v>-2.604919161951347</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.693559141962615</v>
+        <v>1.604212202866658</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.426636228946032</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.6171075320164463</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.340859223628551</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.83873478879454</v>
+        <v>1.749387849698584</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.719556605441195</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.3370627162748123</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.340859223628551</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.835947755134239</v>
+        <v>1.746600816038283</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.679372307075004</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.3206453730404948</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.151763360102433</v>
+        <v>-2.30067492526236</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.860401958041795</v>
+        <v>1.771055018945839</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.5993025115372</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.2892506336046159</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.071693564564629</v>
+        <v>-2.220605129724556</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.907810656585234</v>
+        <v>1.818463717489278</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.3658212893076</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.1879337158749239</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.838212342335031</v>
+        <v>-1.987123907494957</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.055823818760846</v>
+        <v>1.966476879664889</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-8.216154898300086</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.1309593697848772</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.745308851092495</v>
+        <v>-1.894220416252421</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.108673703193408</v>
+        <v>2.019326764097452</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-8.083879424669199</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>-0.08268169358549526</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.613033377461608</v>
+        <v>-1.761944942621535</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.183406474118967</v>
+        <v>2.094059535023011</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.893279749996046</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>-0.003626763028597324</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.571345267948382</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.211234400514539</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.644279951312465</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.1088794976684935</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.571345267948382</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.224140741738198</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.74986994108557</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>-0.06133242783996673</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.676935257721486</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.032810818275117</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.768604843204167</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>-0.02028204681031909</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.676935257721486</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.081355160152203</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.620664801796567</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>-0.08098495293544694</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.656614341812929</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>1.97366878700917</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.603506651665273</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>-0.08283567913640777</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.639456191681634</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>1.975249690834469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.559958244894583</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>-0.07237692852322475</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.639456191681634</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>1.968289078739375</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.317809851440725</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.0389447832394616</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.639456191681634</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>1.982751433120518</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.105668914512453</v>
+        <v>-7.254580479672376</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1183332784699656</v>
+        <v>0.05876865240599605</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.639456191681634</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>1.977283553579714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.982377779695322</v>
+        <v>-7.131289344855245</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1651478264073947</v>
+        <v>0.1055832003434252</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.516165056864504</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.048756328480569</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.961228580791879</v>
+        <v>-7.110140145951802</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.181308484206097</v>
+        <v>0.121743858142128</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.49501585796106</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.06914682605996</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717463138808434</v>
+        <v>-6.866374703968358</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2745953693465255</v>
+        <v>0.2150307432825564</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.49501585796106</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.064927534407011</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.570566111090564</v>
+        <v>-6.719477676250488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3354784943536897</v>
+        <v>0.2759138682897202</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.447357615982472</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.09564679351418</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.320715717141489</v>
+        <v>-6.469627282301413</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4281607269170218</v>
+        <v>0.3685961008530523</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.447357615982472</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.088388868497882</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.144823624674057</v>
+        <v>-6.293735189833981</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5021166874246434</v>
+        <v>0.4425520613606739</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.447357615982472</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.09198799201853</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.973377161651594</v>
+        <v>-6.122288726811518</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5840227786881824</v>
+        <v>0.5244581526242129</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.275911152960009</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.208183375886562</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.748344161982771</v>
+        <v>-5.897255727142695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6730564561720089</v>
+        <v>0.613491830108039</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-1.050878153291186</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.342223653304153</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.684708419748836</v>
+        <v>-5.83361998490876</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7032055541198998</v>
+        <v>0.6436409280559303</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.9872424110572519</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.385099899698831</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.591708378542938</v>
+        <v>-5.740619943702862</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7215998293860548</v>
+        <v>0.6620352033220849</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.9872424110572519</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.366294158482626</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.351277881738078</v>
+        <v>-5.500189446898002</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8195151047328761</v>
+        <v>0.7599504786689066</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.7468119142523916</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.51229553319042</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.279035313566883</v>
+        <v>-5.427946878726807</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8523414458361742</v>
+        <v>0.7927768197722047</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.7468119142523916</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.51622484702524</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.226036991285495</v>
+        <v>-5.374948556445419</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8742193586660694</v>
+        <v>0.8146547326020999</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.6914756552504527</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.550105186343743</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.117232105805768</v>
+        <v>-5.266143670965692</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9147393840779539</v>
+        <v>0.8551747580139839</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.6914756552504527</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.547103257563737</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897211307768758</v>
+        <v>-5.046122872928682</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004326740303372</v>
+        <v>0.9447621142394023</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5502558101824725</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.633414201615139</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.76434361870548</v>
+        <v>-4.913255183865404</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073367998730506</v>
+        <v>1.013803372666537</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.5502558101824725</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.649308384416963</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.60482851518611</v>
+        <v>-4.753740080346034</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138319884578556</v>
+        <v>1.078755258514587</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.3907407066631026</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.746163290968886</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460156370086373</v>
+        <v>-4.609067935246297</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206276845179891</v>
+        <v>1.146712219115921</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.2460685615633652</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.843054680590169</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.520031197444065</v>
+        <v>-4.668942762603989</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16836440563824</v>
+        <v>1.10879977957427</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.3059433889210573</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.793167275576979</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433231699665056</v>
+        <v>-4.58214326482498</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.22548469807241</v>
+        <v>1.16592007200844</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.3059433889210573</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.815567768899546</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435701406126862</v>
+        <v>-4.584612971286786</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.2245692168611</v>
+        <v>1.16500459079713</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.3084130953828634</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.814158346395874</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504071592450872</v>
+        <v>-4.652983157610796</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208228064806197</v>
+        <v>1.148663438742228</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2991373963466485</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.830730688292305</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612609773367006</v>
+        <v>-4.76152133852693</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155249501071635</v>
+        <v>1.095684875007666</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2991373963466485</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.821167396924196</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643602932695711</v>
+        <v>-4.792514497855636</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9675618023805399</v>
+        <v>0.9079971763165702</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2991373963466485</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.645876961964583</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468128672903243</v>
+        <v>-4.617040238063167</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042318738289315</v>
+        <v>0.9827541122253454</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2991373963466485</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.650444193956371</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579064925544492</v>
+        <v>-4.727976490704416</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9736862659940226</v>
+        <v>0.9141216399300529</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.2991373963466485</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.626186222717578</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782091503087725</v>
+        <v>-4.931003068247649</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8956070201966349</v>
+        <v>0.8360423941326651</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.5021639738898819</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.507501661411543</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624165904152432</v>
+        <v>-4.773077469312356</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689496462028844</v>
+        <v>0.9093850201389149</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.5021639738898819</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.517674047843676</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.686834006285978</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983933019872959</v>
+        <v>0.9388286759233262</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.5021639738898819</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.512620318417536</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.583229260525034</v>
+        <v>-4.732140825684958</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9720463496722296</v>
+        <v>0.9124817236082599</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.5429741368991127</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.569256935152479</v>
+        <v>2.479909996056523</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.612262365227335</v>
+        <v>-4.761173930387259</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9609849808244106</v>
+        <v>0.9014203547604409</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.5429741368991127</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569808808185581</v>
+        <v>2.480461869089624</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.631351918162129</v>
+        <v>-4.668363448936399</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8826218515418587</v>
+        <v>0.8678172392321504</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4131521246739802</v>
+        <v>-0.4501636554482533</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.48762776831607</v>
+        <v>2.465420849851506</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.582788865941099</v>
+        <v>-4.61980039671537</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9039205483548713</v>
+        <v>0.8891159360451633</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.36458907245295</v>
+        <v>-0.4016006032272231</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.518639075573288</v>
+        <v>2.496432157108725</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.470117647704849</v>
+        <v>-4.507129178479119</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9440647441610945</v>
+        <v>0.9292601318513862</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2519178542166998</v>
+        <v>-0.2889293849909729</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.581317515026762</v>
+        <v>2.559110596562198</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.357740646522176</v>
+        <v>-4.394752177296446</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.994506840464831</v>
+        <v>0.9797022281551226</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2519178542166998</v>
+        <v>-0.2889293849909729</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.586808810857429</v>
+        <v>2.564601892392865</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.555975215408907</v>
+        <v>-4.592986746183177</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9267102146786776</v>
+        <v>0.9119056023689693</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4501524231034304</v>
+        <v>-0.4871639538777035</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.47936527129393</v>
+        <v>2.457158352829366</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.638976496434186</v>
+        <v>-4.675988027208456</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7318654222692194</v>
+        <v>0.717060809959511</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4687233076306042</v>
+        <v>-0.5057348384048772</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.306578460578279</v>
+        <v>2.284371542113715</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.766043502741174</v>
+        <v>-4.803055033515444</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8011882804656296</v>
+        <v>0.7863836681559215</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4687233076306042</v>
+        <v>-0.5057348384048772</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.426728121297484</v>
+        <v>2.404521202832921</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.852642085722277</v>
+        <v>-4.889653616496547</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7810618733755115</v>
+        <v>0.7662572610658034</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4687233076306042</v>
+        <v>-0.5057348384048772</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.441241147399807</v>
+        <v>2.419034228935244</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.814258423164126</v>
+        <v>-4.851269953938396</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7938347797411407</v>
+        <v>0.7790301674314324</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.430339645072453</v>
+        <v>-0.467351175846726</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.461690786277067</v>
+        <v>2.439483867812503</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.63714209312896</v>
+        <v>-4.67415362390323</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8614103406005089</v>
+        <v>0.8466057282908008</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.430339645072453</v>
+        <v>-0.467351175846726</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.458419815122368</v>
+        <v>2.436212896657805</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.607439969152666</v>
+        <v>-4.644451499926936</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8739745819529396</v>
+        <v>0.8591699696432313</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4348097702877664</v>
+        <v>-0.4718213010620394</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.456421131755094</v>
+        <v>2.43421421329053</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.428064547913898</v>
+        <v>-4.465076078688169</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9395117257548611</v>
+        <v>0.9247071134451528</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2780330121170477</v>
+        <v>-0.3150445428913207</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.544274161963939</v>
+        <v>2.522067243499375</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.473078761434504</v>
+        <v>-4.510090292208774</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9023134956782084</v>
+        <v>0.8875088833685003</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3083819074316523</v>
+        <v>-0.3453934382059253</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.506872280106766</v>
+        <v>2.484665361642203</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.740083271706939</v>
+        <v>-4.777094802481209</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8012032539081801</v>
+        <v>0.7863986415984721</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5027449454746009</v>
+        <v>-0.539756476248874</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.395946019619943</v>
+        <v>2.373739101155379</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.841281053144112</v>
+        <v>-4.878292583918382</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7599280632298124</v>
+        <v>0.7451234509201043</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.57115375901992</v>
+        <v>-0.6081652897941932</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.354104653389253</v>
+        <v>2.331897734924689</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.80880546697334</v>
+        <v>-4.84581699774761</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7705182592524382</v>
+        <v>0.7557136469427299</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.57115375901992</v>
+        <v>-0.6081652897941932</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.35170461494357</v>
+        <v>2.329497696479006</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.789767339266042</v>
+        <v>-4.826778870040313</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.774658229543602</v>
+        <v>0.7598536172338939</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6293373703511146</v>
+        <v>-0.6663489011253877</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.313319167353098</v>
+        <v>2.291112248888534</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.820893970416661</v>
+        <v>-4.857905501190931</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9397894460220351</v>
+        <v>0.924984833712327</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6293373703511146</v>
+        <v>-0.6663489011253877</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.490901036291778</v>
+        <v>2.468694117827214</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.873214351017452</v>
+        <v>-4.910225881791723</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.919694622767852</v>
+        <v>0.9048900104581439</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5943905103422424</v>
+        <v>-0.6314020411165155</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.512702481283235</v>
+        <v>2.490495562818671</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.017537256942371</v>
+        <v>-5.054548787716642</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8679739907948103</v>
+        <v>0.8531693784851022</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5943905103422424</v>
+        <v>-0.6314020411165155</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.518711011680161</v>
+        <v>2.496504093215597</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.869794286707369</v>
+        <v>-4.906805817481639</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.006223826680833</v>
+        <v>0.9914192143711251</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4265831531073593</v>
+        <v>-0.4635946838816324</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.698548073813113</v>
+        <v>2.676341155348549</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.97180896923859</v>
+        <v>-5.00882050001286</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9682115751998257</v>
+        <v>0.9534069628901176</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4265831531073593</v>
+        <v>-0.4635946838816324</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.701341695344594</v>
+        <v>2.67913477688003</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.835199625144497</v>
+        <v>-4.872211155918768</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.023517661229121</v>
+        <v>1.008713048919413</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2899738090132668</v>
+        <v>-0.3269853397875399</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783969650192708</v>
+        <v>2.761762731728144</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.977964957967147</v>
+        <v>-5.014976488741418</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9654920048401714</v>
+        <v>0.9506873925304631</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4327391418359172</v>
+        <v>-0.4697506726101903</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.697390927239228</v>
+        <v>2.675184008774664</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.915666959191025</v>
+        <v>-4.952678489965296</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.056746758147441</v>
+        <v>1.041942145837733</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4327391418359172</v>
+        <v>-0.4697506726101903</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.763726481036048</v>
+        <v>2.741519562571485</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.713876761525867</v>
+        <v>-4.750888292300138</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8460437096029025</v>
+        <v>0.8312390972931942</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2347209496667628</v>
+        <v>-0.2717324804410359</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.591118268726939</v>
+        <v>2.568911350262375</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.653986079883274</v>
+        <v>-4.690997610657544</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.940290214582115</v>
+        <v>0.9254856022724067</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1748302680241693</v>
+        <v>-0.2118417987984424</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.697342910034671</v>
+        <v>2.675135991570107</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.751726624508248</v>
+        <v>-4.788738155282519</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9158217328481688</v>
+        <v>0.9010171205384607</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1907195461571495</v>
+        <v>-0.2277310769314226</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.702437079270926</v>
+        <v>2.680230160806362</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.928064384631178</v>
+        <v>-4.965075915405448</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8438226096236687</v>
+        <v>0.8290179973139606</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3670573062800789</v>
+        <v>-0.404068837054352</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.59517040402184</v>
+        <v>2.572963485557276</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.927375012469954</v>
+        <v>-4.964386543244225</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8425899765280866</v>
+        <v>0.8277853642183786</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3670573062800789</v>
+        <v>-0.404068837054352</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.593662022061769</v>
+        <v>2.571455103597205</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.933945977524547</v>
+        <v>-4.970957508298818</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8398244579416858</v>
+        <v>0.8250198456319775</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3736282713346719</v>
+        <v>-0.410639802108945</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.589582310464449</v>
+        <v>2.567375391999885</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.925992007229775</v>
+        <v>-4.963003538004045</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8430060460595947</v>
+        <v>0.8282014337498864</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3736282713346719</v>
+        <v>-0.410639802108945</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.589582310464449</v>
+        <v>2.567375391999885</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.915618630896688</v>
+        <v>-4.952630161670958</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.853537153620634</v>
+        <v>0.8387325413109259</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3632548950015846</v>
+        <v>-0.4002664257758577</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.602188093292106</v>
+        <v>2.579981174827542</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.787934321102392</v>
+        <v>-4.824945851876662</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9095032509130774</v>
+        <v>0.8946986386033693</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2355705852072881</v>
+        <v>-0.2725821159815612</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.683691052543409</v>
+        <v>2.661484134078845</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.511965621676836</v>
+        <v>3.583875037956185</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.687564729023019</v>
+        <v>-4.733087850368036</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9364057602206988</v>
+        <v>0.918196511682692</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.29181095500698</v>
+        <v>-0.3012042996097559</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.636701503139466</v>
+        <v>2.6310654963778</v>
       </c>
     </row>
   </sheetData>
